--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>상장일</t>
   </si>
@@ -118,162 +118,153 @@
     <t>2024-06-19</t>
   </si>
   <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>아이빔테크놀로지</t>
+  </si>
+  <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
+    <t>SK증권제13호스팩</t>
+  </si>
+  <si>
+    <t>엑셀세라퓨틱스</t>
+  </si>
+  <si>
+    <t>시프트업</t>
+  </si>
+  <si>
+    <t>이베스트스팩6호</t>
+  </si>
+  <si>
+    <t>하스</t>
+  </si>
+  <si>
+    <t>이노스페이스</t>
+  </si>
+  <si>
+    <t>에이치브이엠</t>
+  </si>
+  <si>
+    <t>하이젠알앤엠</t>
+  </si>
+  <si>
+    <t>한국제15호스팩</t>
+  </si>
+  <si>
+    <t>에스오에스랩</t>
+  </si>
+  <si>
+    <t>미래에셋비전스팩6호</t>
+  </si>
+  <si>
+    <t>KB제29호스팩</t>
+  </si>
+  <si>
+    <t>에이치엠씨제7호스팩</t>
+  </si>
+  <si>
+    <t>한국제14호스팩</t>
+  </si>
+  <si>
+    <t>미래에셋비전스팩5호</t>
+  </si>
+  <si>
+    <t>씨어스테크놀로지</t>
+  </si>
+  <si>
+    <t>한중엔시에스</t>
+  </si>
+  <si>
+    <t>신한글로벌액티브리츠</t>
+  </si>
+  <si>
+    <t>코스닥</t>
+  </si>
+  <si>
+    <t>코스피</t>
+  </si>
+  <si>
+    <t>삼성</t>
+  </si>
+  <si>
+    <t>키움</t>
+  </si>
+  <si>
+    <t>미래</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>대신</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>제이피모간회사</t>
+  </si>
+  <si>
+    <t>신한</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>BNK</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>현대차</t>
+  </si>
+  <si>
+    <t>IBK</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>대표</t>
+  </si>
+  <si>
+    <t>인수</t>
+  </si>
+  <si>
+    <t>공동대표</t>
+  </si>
+  <si>
+    <t>2024-07-22</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
+    <t>2024-06-20</t>
+  </si>
+  <si>
+    <t>2024-06-18</t>
+  </si>
+  <si>
     <t>2024-06-17</t>
   </si>
   <si>
-    <t>2024-06-18</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>아이빔테크놀로지</t>
-  </si>
-  <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
-    <t>시프트업</t>
-  </si>
-  <si>
-    <t>이베스트스팩6호</t>
-  </si>
-  <si>
-    <t>하스</t>
-  </si>
-  <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
-    <t>에이치브이엠</t>
-  </si>
-  <si>
-    <t>하이젠알앤엠</t>
-  </si>
-  <si>
-    <t>한국제15호스팩</t>
-  </si>
-  <si>
-    <t>에스오에스랩</t>
-  </si>
-  <si>
-    <t>미래에셋비전스팩6호</t>
-  </si>
-  <si>
-    <t>KB제29호스팩</t>
-  </si>
-  <si>
-    <t>에이치엠씨제7호스팩</t>
-  </si>
-  <si>
-    <t>한국제14호스팩</t>
-  </si>
-  <si>
-    <t>미래에셋비전스팩5호</t>
-  </si>
-  <si>
-    <t>씨어스테크놀로지</t>
-  </si>
-  <si>
-    <t>한중엔시에스</t>
-  </si>
-  <si>
-    <t>라메디텍</t>
-  </si>
-  <si>
-    <t>디비금융스팩12호</t>
-  </si>
-  <si>
-    <t>신한글로벌액티브리츠</t>
-  </si>
-  <si>
-    <t>코스닥</t>
-  </si>
-  <si>
-    <t>코스피</t>
-  </si>
-  <si>
-    <t>삼성</t>
-  </si>
-  <si>
-    <t>키움</t>
-  </si>
-  <si>
-    <t>미래</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>대신</t>
-  </si>
-  <si>
-    <t>한국</t>
-  </si>
-  <si>
-    <t>제이피모간회사</t>
-  </si>
-  <si>
-    <t>신한</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>BNK</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>현대차</t>
-  </si>
-  <si>
-    <t>IBK</t>
-  </si>
-  <si>
-    <t>DB</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>대표</t>
-  </si>
-  <si>
-    <t>인수</t>
-  </si>
-  <si>
-    <t>공동대표</t>
-  </si>
-  <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
-    <t>2024-06-20</t>
-  </si>
-  <si>
     <t>2024-06-14</t>
   </si>
   <si>
@@ -284,9 +275,6 @@
   </si>
   <si>
     <t>2024-06-10</t>
-  </si>
-  <si>
-    <t>2024-06-05</t>
   </si>
   <si>
     <t>2024-07-30</t>
@@ -659,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -720,37 +708,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>223.4</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>223.4</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M2">
         <v>10000</v>
@@ -762,7 +750,7 @@
         <v>21</v>
       </c>
       <c r="P2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="Q2">
         <v>1675500</v>
@@ -773,37 +761,37 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D3">
         <v>297</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>297</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M3">
         <v>22000</v>
@@ -812,7 +800,7 @@
         <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="P3" t="s">
         <v>21</v>
@@ -826,37 +814,37 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D4">
         <v>2660</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F4">
         <v>2553.6</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M4">
         <v>35000</v>
@@ -865,10 +853,10 @@
         <v>96</v>
       </c>
       <c r="O4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="P4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q4">
         <v>9340690</v>
@@ -879,37 +867,37 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D5">
         <v>2660</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F5">
         <v>106.4</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M5">
         <v>35000</v>
@@ -918,10 +906,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="P5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q5">
         <v>9340690</v>
@@ -932,37 +920,37 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D6">
         <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F6">
         <v>120</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M6">
         <v>2000</v>
@@ -971,10 +959,10 @@
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="Q6">
         <v>4500000</v>
@@ -985,37 +973,37 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F7">
         <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M7">
         <v>2000</v>
@@ -1027,7 +1015,7 @@
         <v>22</v>
       </c>
       <c r="P7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="Q7">
         <v>3000000</v>
@@ -1038,37 +1026,37 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>161.8</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F8">
         <v>161.8</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M8">
         <v>10000</v>
@@ -1080,7 +1068,7 @@
         <v>25</v>
       </c>
       <c r="P8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="Q8">
         <v>1187900</v>
@@ -1091,37 +1079,37 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D9">
         <v>4350</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F9">
         <v>1435.5</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M9">
         <v>60000</v>
@@ -1133,7 +1121,7 @@
         <v>26</v>
       </c>
       <c r="P9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="Q9">
         <v>21750000</v>
@@ -1144,37 +1132,37 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>4350</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F10">
         <v>1435.5</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M10">
         <v>60000</v>
@@ -1186,7 +1174,7 @@
         <v>26</v>
       </c>
       <c r="P10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="Q10">
         <v>21750000</v>
@@ -1197,37 +1185,37 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D11">
         <v>4350</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F11">
         <v>1305</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M11">
         <v>60000</v>
@@ -1239,7 +1227,7 @@
         <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="Q11">
         <v>21750000</v>
@@ -1250,37 +1238,37 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D12">
         <v>4350</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F12">
         <v>174</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M12">
         <v>60000</v>
@@ -1292,7 +1280,7 @@
         <v>26</v>
       </c>
       <c r="P12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="Q12">
         <v>21750000</v>
@@ -1303,37 +1291,37 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D13">
         <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F13">
         <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M13">
         <v>2000</v>
@@ -1345,7 +1333,7 @@
         <v>26</v>
       </c>
       <c r="P13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="Q13">
         <v>3000000</v>
@@ -1356,37 +1344,37 @@
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D14">
         <v>289.6</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F14">
         <v>289.6</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M14">
         <v>16000</v>
@@ -1409,37 +1397,37 @@
         <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D15">
         <v>575.89</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F15">
         <v>541.3366</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M15">
         <v>43300</v>
@@ -1448,7 +1436,7 @@
         <v>94</v>
       </c>
       <c r="O15" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="P15" t="s">
         <v>30</v>
@@ -1462,37 +1450,37 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D16">
         <v>575.89</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F16">
         <v>34.5534</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M16">
         <v>43300</v>
@@ -1501,7 +1489,7 @@
         <v>6</v>
       </c>
       <c r="O16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="P16" t="s">
         <v>30</v>
@@ -1515,37 +1503,37 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D17">
         <v>432</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F17">
         <v>432</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M17">
         <v>18000</v>
@@ -1568,37 +1556,37 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D18">
         <v>238</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F18">
         <v>238</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M18">
         <v>7000</v>
@@ -1607,7 +1595,7 @@
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="P18" t="s">
         <v>32</v>
@@ -1621,37 +1609,37 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F19">
         <v>125</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K19" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M19">
         <v>2000</v>
@@ -1660,10 +1648,10 @@
         <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="P19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Q19">
         <v>4687500</v>
@@ -1674,37 +1662,37 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D20">
         <v>230</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F20">
         <v>218.5</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M20">
         <v>11500</v>
@@ -1713,7 +1701,7 @@
         <v>95</v>
       </c>
       <c r="O20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P20" t="s">
         <v>33</v>
@@ -1727,37 +1715,37 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D21">
         <v>230</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F21">
         <v>11.5</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M21">
         <v>11500</v>
@@ -1766,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P21" t="s">
         <v>33</v>
@@ -1780,37 +1768,37 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D22">
         <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F22">
         <v>129</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M22">
         <v>2000</v>
@@ -1819,10 +1807,10 @@
         <v>100</v>
       </c>
       <c r="O22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P22" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="Q22">
         <v>4837500</v>
@@ -1833,37 +1821,37 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D23">
         <v>120</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F23">
         <v>120</v>
       </c>
       <c r="G23" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J23" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K23" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L23" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M23">
         <v>2000</v>
@@ -1872,10 +1860,10 @@
         <v>100</v>
       </c>
       <c r="O23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Q23">
         <v>4500000</v>
@@ -1886,37 +1874,37 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>140</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F24">
         <v>140</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K24" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M24">
         <v>2000</v>
@@ -1925,10 +1913,10 @@
         <v>100</v>
       </c>
       <c r="O24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Q24">
         <v>5250000</v>
@@ -1939,37 +1927,37 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D25">
         <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F25">
         <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K25" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M25">
         <v>2000</v>
@@ -1978,10 +1966,10 @@
         <v>100</v>
       </c>
       <c r="O25" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q25">
         <v>3000000</v>
@@ -1992,37 +1980,37 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>95</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F26">
         <v>95</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H26" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J26" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L26" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M26">
         <v>2000</v>
@@ -2031,10 +2019,10 @@
         <v>100</v>
       </c>
       <c r="O26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q26">
         <v>3562500</v>
@@ -2045,37 +2033,37 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D27">
         <v>221</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F27">
         <v>221</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K27" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M27">
         <v>17000</v>
@@ -2084,10 +2072,10 @@
         <v>100</v>
       </c>
       <c r="O27" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q27">
         <v>975000</v>
@@ -2098,37 +2086,37 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
         <v>57</v>
-      </c>
-      <c r="C28" t="s">
-        <v>61</v>
       </c>
       <c r="D28">
         <v>480</v>
       </c>
       <c r="E28" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F28">
         <v>480</v>
       </c>
       <c r="G28" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H28" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J28" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L28" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M28">
         <v>30000</v>
@@ -2137,10 +2125,10 @@
         <v>100</v>
       </c>
       <c r="O28" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q28">
         <v>1123925</v>
@@ -2151,210 +2139,104 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
         <v>58</v>
       </c>
-      <c r="C29" t="s">
-        <v>61</v>
-      </c>
       <c r="D29">
-        <v>207.68</v>
+        <v>700.0000199999999</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F29">
-        <v>207.68</v>
+        <v>350.00001</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M29">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O29" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P29" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="Q29">
-        <v>957220</v>
+        <v>32666668</v>
       </c>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D30">
-        <v>100</v>
+        <v>700.0000199999999</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>350.00001</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M30">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O30" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P30" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="Q30">
-        <v>3750000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31">
-        <v>700.0000199999999</v>
-      </c>
-      <c r="E31" t="s">
-        <v>71</v>
-      </c>
-      <c r="F31">
-        <v>350.00001</v>
-      </c>
-      <c r="G31" t="s">
-        <v>78</v>
-      </c>
-      <c r="H31" t="s">
-        <v>78</v>
-      </c>
-      <c r="I31" t="s">
-        <v>78</v>
-      </c>
-      <c r="J31" t="s">
-        <v>78</v>
-      </c>
-      <c r="K31" t="s">
-        <v>81</v>
-      </c>
-      <c r="L31" t="s">
-        <v>78</v>
-      </c>
-      <c r="M31">
-        <v>3000</v>
-      </c>
-      <c r="N31">
-        <v>50</v>
-      </c>
-      <c r="O31" t="s">
-        <v>87</v>
-      </c>
-      <c r="P31" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q31">
-        <v>32666668</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32">
-        <v>700.0000199999999</v>
-      </c>
-      <c r="E32" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32">
-        <v>350.00001</v>
-      </c>
-      <c r="G32" t="s">
-        <v>78</v>
-      </c>
-      <c r="H32" t="s">
-        <v>78</v>
-      </c>
-      <c r="I32" t="s">
-        <v>78</v>
-      </c>
-      <c r="J32" t="s">
-        <v>78</v>
-      </c>
-      <c r="K32" t="s">
-        <v>81</v>
-      </c>
-      <c r="L32" t="s">
-        <v>78</v>
-      </c>
-      <c r="M32">
-        <v>3000</v>
-      </c>
-      <c r="N32">
-        <v>50</v>
-      </c>
-      <c r="O32" t="s">
-        <v>87</v>
-      </c>
-      <c r="P32" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q32">
         <v>32666668</v>
       </c>
     </row>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="89">
   <si>
     <t>상장일</t>
   </si>
@@ -67,6 +67,9 @@
     <t>총기관배정수량</t>
   </si>
   <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
     <t>2024-08-06</t>
   </si>
   <si>
@@ -115,150 +118,141 @@
     <t>2024-06-21</t>
   </si>
   <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
+    <t>아이빔테크놀로지</t>
+  </si>
+  <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
+    <t>SK증권제13호스팩</t>
+  </si>
+  <si>
+    <t>엑셀세라퓨틱스</t>
+  </si>
+  <si>
+    <t>시프트업</t>
+  </si>
+  <si>
+    <t>이베스트스팩6호</t>
+  </si>
+  <si>
+    <t>하스</t>
+  </si>
+  <si>
+    <t>이노스페이스</t>
+  </si>
+  <si>
+    <t>에이치브이엠</t>
+  </si>
+  <si>
+    <t>하이젠알앤엠</t>
+  </si>
+  <si>
+    <t>한국제15호스팩</t>
+  </si>
+  <si>
+    <t>에스오에스랩</t>
+  </si>
+  <si>
+    <t>미래에셋비전스팩6호</t>
+  </si>
+  <si>
+    <t>KB제29호스팩</t>
+  </si>
+  <si>
+    <t>에이치엠씨제7호스팩</t>
+  </si>
+  <si>
+    <t>신한글로벌액티브리츠</t>
+  </si>
+  <si>
+    <t>코스닥</t>
+  </si>
+  <si>
+    <t>코스피</t>
+  </si>
+  <si>
+    <t>미래</t>
+  </si>
+  <si>
+    <t>삼성</t>
+  </si>
+  <si>
+    <t>키움</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>대신</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>제이피모간회사</t>
+  </si>
+  <si>
+    <t>신한</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>BNK</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>현대차</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>대표</t>
+  </si>
+  <si>
+    <t>인수</t>
+  </si>
+  <si>
+    <t>공동대표</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
+    <t>2024-07-22</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
+    <t>2024-06-20</t>
+  </si>
+  <si>
     <t>2024-06-19</t>
   </si>
   <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>아이빔테크놀로지</t>
-  </si>
-  <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
-    <t>시프트업</t>
-  </si>
-  <si>
-    <t>이베스트스팩6호</t>
-  </si>
-  <si>
-    <t>하스</t>
-  </si>
-  <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
-    <t>에이치브이엠</t>
-  </si>
-  <si>
-    <t>하이젠알앤엠</t>
-  </si>
-  <si>
-    <t>한국제15호스팩</t>
-  </si>
-  <si>
-    <t>에스오에스랩</t>
-  </si>
-  <si>
-    <t>미래에셋비전스팩6호</t>
-  </si>
-  <si>
-    <t>KB제29호스팩</t>
-  </si>
-  <si>
-    <t>에이치엠씨제7호스팩</t>
-  </si>
-  <si>
-    <t>한국제14호스팩</t>
-  </si>
-  <si>
-    <t>미래에셋비전스팩5호</t>
-  </si>
-  <si>
-    <t>씨어스테크놀로지</t>
-  </si>
-  <si>
-    <t>한중엔시에스</t>
-  </si>
-  <si>
-    <t>신한글로벌액티브리츠</t>
-  </si>
-  <si>
-    <t>코스닥</t>
-  </si>
-  <si>
-    <t>코스피</t>
-  </si>
-  <si>
-    <t>삼성</t>
-  </si>
-  <si>
-    <t>키움</t>
-  </si>
-  <si>
-    <t>미래</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>대신</t>
-  </si>
-  <si>
-    <t>한국</t>
-  </si>
-  <si>
-    <t>제이피모간회사</t>
-  </si>
-  <si>
-    <t>신한</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>BNK</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>현대차</t>
-  </si>
-  <si>
-    <t>IBK</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>대표</t>
-  </si>
-  <si>
-    <t>인수</t>
-  </si>
-  <si>
-    <t>공동대표</t>
-  </si>
-  <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
-    <t>2024-06-20</t>
-  </si>
-  <si>
     <t>2024-06-18</t>
   </si>
   <si>
@@ -272,9 +266,6 @@
   </si>
   <si>
     <t>2024-06-11</t>
-  </si>
-  <si>
-    <t>2024-06-10</t>
   </si>
   <si>
     <t>2024-07-30</t>
@@ -647,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -711,49 +702,49 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D2">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F2">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M2">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N2">
         <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="P2" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="Q2">
-        <v>1675500</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -764,49 +755,49 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3">
+        <v>223.4</v>
+      </c>
+      <c r="E3" t="s">
         <v>57</v>
       </c>
-      <c r="D3">
-        <v>297</v>
-      </c>
-      <c r="E3" t="s">
-        <v>60</v>
-      </c>
       <c r="F3">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M3">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N3">
         <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="Q3">
-        <v>1012500</v>
+        <v>1675500</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -817,99 +808,99 @@
         <v>37</v>
       </c>
       <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4">
+        <v>297</v>
+      </c>
+      <c r="E4" t="s">
         <v>58</v>
       </c>
-      <c r="D4">
-        <v>2660</v>
-      </c>
-      <c r="E4" t="s">
-        <v>61</v>
-      </c>
       <c r="F4">
-        <v>2553.6</v>
+        <v>297</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4">
+        <v>22000</v>
+      </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4" t="s">
         <v>74</v>
       </c>
-      <c r="L4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4">
-        <v>35000</v>
-      </c>
-      <c r="N4">
-        <v>96</v>
-      </c>
-      <c r="O4" t="s">
-        <v>78</v>
-      </c>
       <c r="P4" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="Q4">
-        <v>9340690</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D5">
         <v>2660</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F5">
-        <v>106.4</v>
+        <v>2553.6</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M5">
         <v>35000</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="O5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q5">
         <v>9340690</v>
@@ -923,49 +914,49 @@
         <v>38</v>
       </c>
       <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6">
+        <v>2660</v>
+      </c>
+      <c r="E6" t="s">
         <v>57</v>
       </c>
-      <c r="D6">
-        <v>120</v>
-      </c>
-      <c r="E6" t="s">
-        <v>62</v>
-      </c>
       <c r="F6">
-        <v>120</v>
+        <v>106.4</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="Q6">
-        <v>4500000</v>
+        <v>9340690</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -976,34 +967,34 @@
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M7">
         <v>2000</v>
@@ -1012,13 +1003,13 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="P7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q7">
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1029,49 +1020,49 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F8">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M8">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P8" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Q8">
-        <v>1187900</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1082,87 +1073,87 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D9">
-        <v>4350</v>
+        <v>161.8</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F9">
-        <v>1435.5</v>
+        <v>161.8</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M9">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="N9">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="O9" t="s">
         <v>26</v>
       </c>
       <c r="P9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="Q9">
-        <v>21750000</v>
+        <v>1187900</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D10">
         <v>4350</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F10">
         <v>1435.5</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M10">
         <v>60000</v>
@@ -1171,10 +1162,10 @@
         <v>33</v>
       </c>
       <c r="O10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q10">
         <v>21750000</v>
@@ -1182,52 +1173,52 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D11">
         <v>4350</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11">
-        <v>1305</v>
+        <v>1435.5</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M11">
         <v>60000</v>
       </c>
       <c r="N11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q11">
         <v>21750000</v>
@@ -1235,52 +1226,52 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>4350</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F12">
-        <v>174</v>
+        <v>1305</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M12">
         <v>60000</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q12">
         <v>21750000</v>
@@ -1294,49 +1285,49 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13">
-        <v>80</v>
+        <v>4350</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q13">
-        <v>3000000</v>
+        <v>21750000</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1347,49 +1338,49 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14">
-        <v>289.6</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F14">
-        <v>289.6</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M14">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P14" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="Q14">
-        <v>1357500</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1400,99 +1391,99 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15">
+        <v>289.6</v>
+      </c>
+      <c r="E15" t="s">
         <v>57</v>
       </c>
-      <c r="D15">
-        <v>575.89</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
-      </c>
       <c r="F15">
-        <v>541.3366</v>
+        <v>289.6</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M15">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N15">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="P15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q15">
-        <v>1906400</v>
+        <v>1357500</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D16">
         <v>575.89</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F16">
-        <v>34.5534</v>
+        <v>541.3366</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K16" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M16">
         <v>43300</v>
       </c>
       <c r="N16">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="O16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q16">
         <v>1906400</v>
@@ -1506,49 +1497,49 @@
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D17">
-        <v>432</v>
+        <v>575.89</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17">
-        <v>432</v>
+        <v>34.5534</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M17">
-        <v>18000</v>
+        <v>43300</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="O17" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="P17" t="s">
         <v>31</v>
       </c>
       <c r="Q17">
-        <v>1758600</v>
+        <v>1906400</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1559,49 +1550,49 @@
         <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18">
-        <v>238</v>
+        <v>432</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F18">
-        <v>238</v>
+        <v>432</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K18" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M18">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P18" t="s">
         <v>32</v>
       </c>
       <c r="Q18">
-        <v>2350000</v>
+        <v>1758600</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1612,49 +1603,49 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F19">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M19">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P19" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="Q19">
-        <v>4687500</v>
+        <v>2350000</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1665,99 +1656,99 @@
         <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D20">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F20">
-        <v>218.5</v>
+        <v>125</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K20" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M20">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N20">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P20" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="Q20">
-        <v>3000000</v>
+        <v>4687500</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <v>230</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F21">
-        <v>11.5</v>
+        <v>218.5</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K21" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M21">
         <v>11500</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="O21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="Q21">
         <v>3000000</v>
@@ -1771,49 +1762,49 @@
         <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D22">
-        <v>129</v>
+        <v>230</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F22">
-        <v>129</v>
+        <v>11.5</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M22">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Q22">
-        <v>4837500</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1824,34 +1815,34 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D23">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23">
+        <v>129</v>
+      </c>
+      <c r="G23" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" t="s">
+        <v>69</v>
+      </c>
+      <c r="J23" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" t="s">
         <v>70</v>
       </c>
-      <c r="F23">
-        <v>120</v>
-      </c>
-      <c r="G23" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" t="s">
-        <v>73</v>
-      </c>
-      <c r="I23" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" t="s">
-        <v>73</v>
-      </c>
-      <c r="K23" t="s">
-        <v>74</v>
-      </c>
       <c r="L23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M23">
         <v>2000</v>
@@ -1860,51 +1851,51 @@
         <v>100</v>
       </c>
       <c r="O23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P23" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="Q23">
-        <v>4500000</v>
+        <v>4837500</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D24">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F24">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K24" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M24">
         <v>2000</v>
@@ -1913,51 +1904,51 @@
         <v>100</v>
       </c>
       <c r="O24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q24">
-        <v>5250000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
         <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D25">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F25">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K25" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M25">
         <v>2000</v>
@@ -1966,277 +1957,118 @@
         <v>100</v>
       </c>
       <c r="O25" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q25">
-        <v>3000000</v>
+        <v>5250000</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
         <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D26">
-        <v>95</v>
+        <v>700.0000199999999</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F26">
-        <v>95</v>
+        <v>350.00001</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M26">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O26" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="Q26">
-        <v>3562500</v>
+        <v>32666668</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27">
-        <v>221</v>
+        <v>700.0000199999999</v>
       </c>
       <c r="E27" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F27">
-        <v>221</v>
+        <v>350.00001</v>
       </c>
       <c r="G27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M27">
-        <v>17000</v>
+        <v>3000</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O27" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="Q27">
-        <v>975000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28">
-        <v>480</v>
-      </c>
-      <c r="E28" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28">
-        <v>480</v>
-      </c>
-      <c r="G28" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" t="s">
-        <v>73</v>
-      </c>
-      <c r="I28" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28" t="s">
-        <v>73</v>
-      </c>
-      <c r="K28" t="s">
-        <v>74</v>
-      </c>
-      <c r="L28" t="s">
-        <v>73</v>
-      </c>
-      <c r="M28">
-        <v>30000</v>
-      </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
-      <c r="O28" t="s">
-        <v>86</v>
-      </c>
-      <c r="P28" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q28">
-        <v>1123925</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29">
-        <v>700.0000199999999</v>
-      </c>
-      <c r="E29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29">
-        <v>350.00001</v>
-      </c>
-      <c r="G29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" t="s">
-        <v>73</v>
-      </c>
-      <c r="I29" t="s">
-        <v>73</v>
-      </c>
-      <c r="J29" t="s">
-        <v>73</v>
-      </c>
-      <c r="K29" t="s">
-        <v>76</v>
-      </c>
-      <c r="L29" t="s">
-        <v>73</v>
-      </c>
-      <c r="M29">
-        <v>3000</v>
-      </c>
-      <c r="N29">
-        <v>50</v>
-      </c>
-      <c r="O29" t="s">
-        <v>84</v>
-      </c>
-      <c r="P29" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q29">
-        <v>32666668</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17">
-      <c r="A30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30">
-        <v>700.0000199999999</v>
-      </c>
-      <c r="E30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30">
-        <v>350.00001</v>
-      </c>
-      <c r="G30" t="s">
-        <v>73</v>
-      </c>
-      <c r="H30" t="s">
-        <v>73</v>
-      </c>
-      <c r="I30" t="s">
-        <v>73</v>
-      </c>
-      <c r="J30" t="s">
-        <v>73</v>
-      </c>
-      <c r="K30" t="s">
-        <v>76</v>
-      </c>
-      <c r="L30" t="s">
-        <v>73</v>
-      </c>
-      <c r="M30">
-        <v>3000</v>
-      </c>
-      <c r="N30">
-        <v>50</v>
-      </c>
-      <c r="O30" t="s">
-        <v>84</v>
-      </c>
-      <c r="P30" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q30">
         <v>32666668</v>
       </c>
     </row>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="87">
   <si>
     <t>상장일</t>
   </si>
@@ -67,6 +67,9 @@
     <t>총기관배정수량</t>
   </si>
   <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
     <t>2024-08-12</t>
   </si>
   <si>
@@ -115,172 +118,163 @@
     <t>2024-06-24</t>
   </si>
   <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>교보16호스팩</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
+    <t>아이빔테크놀로지</t>
+  </si>
+  <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
+    <t>SK증권제13호스팩</t>
+  </si>
+  <si>
+    <t>엑셀세라퓨틱스</t>
+  </si>
+  <si>
+    <t>시프트업</t>
+  </si>
+  <si>
+    <t>이베스트스팩6호</t>
+  </si>
+  <si>
+    <t>하스</t>
+  </si>
+  <si>
+    <t>이노스페이스</t>
+  </si>
+  <si>
+    <t>에이치브이엠</t>
+  </si>
+  <si>
+    <t>하이젠알앤엠</t>
+  </si>
+  <si>
+    <t>한국제15호스팩</t>
+  </si>
+  <si>
+    <t>에스오에스랩</t>
+  </si>
+  <si>
+    <t>미래에셋비전스팩6호</t>
+  </si>
+  <si>
+    <t>신한글로벌액티브리츠</t>
+  </si>
+  <si>
+    <t>코스닥</t>
+  </si>
+  <si>
+    <t>코스피</t>
+  </si>
+  <si>
+    <t>교보</t>
+  </si>
+  <si>
+    <t>미래</t>
+  </si>
+  <si>
+    <t>삼성</t>
+  </si>
+  <si>
+    <t>키움</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>대신</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>제이피모간회사</t>
+  </si>
+  <si>
+    <t>신한</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>BNK</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>대표</t>
+  </si>
+  <si>
+    <t>인수</t>
+  </si>
+  <si>
+    <t>공동대표</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
+    <t>2024-07-22</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
+    <t>2024-06-20</t>
+  </si>
+  <si>
+    <t>2024-06-19</t>
+  </si>
+  <si>
+    <t>2024-06-18</t>
+  </si>
+  <si>
+    <t>2024-06-17</t>
+  </si>
+  <si>
+    <t>2024-06-14</t>
+  </si>
+  <si>
+    <t>2024-06-13</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>2024-07-23</t>
+  </si>
+  <si>
+    <t>2024-07-19</t>
+  </si>
+  <si>
+    <t>2024-07-08</t>
+  </si>
+  <si>
+    <t>2024-07-05</t>
+  </si>
+  <si>
     <t>2024-06-21</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
-    <t>아이빔테크놀로지</t>
-  </si>
-  <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
-    <t>시프트업</t>
-  </si>
-  <si>
-    <t>이베스트스팩6호</t>
-  </si>
-  <si>
-    <t>하스</t>
-  </si>
-  <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
-    <t>에이치브이엠</t>
-  </si>
-  <si>
-    <t>하이젠알앤엠</t>
-  </si>
-  <si>
-    <t>한국제15호스팩</t>
-  </si>
-  <si>
-    <t>에스오에스랩</t>
-  </si>
-  <si>
-    <t>미래에셋비전스팩6호</t>
-  </si>
-  <si>
-    <t>KB제29호스팩</t>
-  </si>
-  <si>
-    <t>에이치엠씨제7호스팩</t>
-  </si>
-  <si>
-    <t>신한글로벌액티브리츠</t>
-  </si>
-  <si>
-    <t>코스닥</t>
-  </si>
-  <si>
-    <t>코스피</t>
-  </si>
-  <si>
-    <t>미래</t>
-  </si>
-  <si>
-    <t>삼성</t>
-  </si>
-  <si>
-    <t>키움</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>대신</t>
-  </si>
-  <si>
-    <t>한국</t>
-  </si>
-  <si>
-    <t>제이피모간회사</t>
-  </si>
-  <si>
-    <t>신한</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>BNK</t>
-  </si>
-  <si>
-    <t>KB</t>
-  </si>
-  <si>
-    <t>현대차</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>대표</t>
-  </si>
-  <si>
-    <t>인수</t>
-  </si>
-  <si>
-    <t>공동대표</t>
-  </si>
-  <si>
-    <t>2024-08-01</t>
-  </si>
-  <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
-    <t>2024-06-20</t>
-  </si>
-  <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
-    <t>2024-06-18</t>
-  </si>
-  <si>
-    <t>2024-06-17</t>
-  </si>
-  <si>
-    <t>2024-06-14</t>
-  </si>
-  <si>
-    <t>2024-06-13</t>
-  </si>
-  <si>
-    <t>2024-06-11</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>2024-07-23</t>
-  </si>
-  <si>
-    <t>2024-07-19</t>
-  </si>
-  <si>
-    <t>2024-07-08</t>
-  </si>
-  <si>
-    <t>2024-07-05</t>
   </si>
 </sst>
 </file>
@@ -638,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -702,49 +696,49 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M2">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N2">
         <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q2">
-        <v>1050000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -755,49 +749,49 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M3">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N3">
         <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="Q3">
-        <v>1675500</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -808,49 +802,49 @@
         <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F4">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M4">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="P4" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="Q4">
-        <v>1012500</v>
+        <v>1675500</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -861,99 +855,99 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>2660</v>
+        <v>297</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>2553.6</v>
+        <v>297</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M5">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="N5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="Q5">
-        <v>9340690</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>2660</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F6">
-        <v>106.4</v>
+        <v>2553.6</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M6">
         <v>35000</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="O6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Q6">
         <v>9340690</v>
@@ -970,46 +964,46 @@
         <v>54</v>
       </c>
       <c r="D7">
-        <v>120</v>
+        <v>2660</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>120</v>
+        <v>106.4</v>
       </c>
       <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" t="s">
         <v>69</v>
       </c>
-      <c r="H7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
-      </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M7">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="Q7">
-        <v>4500000</v>
+        <v>9340690</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1020,34 +1014,34 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M8">
         <v>2000</v>
@@ -1056,13 +1050,13 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="Q8">
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1073,49 +1067,49 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F9">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M9">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P9" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="Q9">
-        <v>1187900</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1126,87 +1120,87 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>4350</v>
+        <v>161.8</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F10">
-        <v>1435.5</v>
+        <v>161.8</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M10">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="N10">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="O10" t="s">
         <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="Q10">
-        <v>21750000</v>
+        <v>1187900</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11">
         <v>4350</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F11">
         <v>1435.5</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M11">
         <v>60000</v>
@@ -1215,10 +1209,10 @@
         <v>33</v>
       </c>
       <c r="O11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q11">
         <v>21750000</v>
@@ -1226,52 +1220,52 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12">
         <v>4350</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F12">
-        <v>1305</v>
+        <v>1435.5</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M12">
         <v>60000</v>
       </c>
       <c r="N12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q12">
         <v>21750000</v>
@@ -1279,52 +1273,52 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13">
         <v>4350</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F13">
-        <v>174</v>
+        <v>1305</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M13">
         <v>60000</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q13">
         <v>21750000</v>
@@ -1341,46 +1335,46 @@
         <v>54</v>
       </c>
       <c r="D14">
-        <v>80</v>
+        <v>4350</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" t="s">
         <v>69</v>
       </c>
-      <c r="H14" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" t="s">
-        <v>69</v>
-      </c>
-      <c r="K14" t="s">
-        <v>70</v>
-      </c>
       <c r="L14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M14">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q14">
-        <v>3000000</v>
+        <v>21750000</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1391,49 +1385,49 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15">
-        <v>289.6</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F15">
-        <v>289.6</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M15">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P15" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="Q15">
-        <v>1357500</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1444,99 +1438,99 @@
         <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16">
-        <v>575.89</v>
+        <v>289.6</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F16">
-        <v>541.3366</v>
+        <v>289.6</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M16">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N16">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="P16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q16">
-        <v>1906400</v>
+        <v>1357500</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17">
         <v>575.89</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F17">
-        <v>34.5534</v>
+        <v>541.3366</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M17">
         <v>43300</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="O17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q17">
         <v>1906400</v>
@@ -1550,49 +1544,49 @@
         <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18">
-        <v>432</v>
+        <v>575.89</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F18">
-        <v>432</v>
+        <v>34.5534</v>
       </c>
       <c r="G18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" t="s">
+        <v>67</v>
+      </c>
+      <c r="K18" t="s">
         <v>69</v>
       </c>
-      <c r="H18" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" t="s">
-        <v>69</v>
-      </c>
-      <c r="K18" t="s">
-        <v>70</v>
-      </c>
       <c r="L18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M18">
-        <v>18000</v>
+        <v>43300</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="O18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P18" t="s">
         <v>32</v>
       </c>
       <c r="Q18">
-        <v>1758600</v>
+        <v>1906400</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1603,49 +1597,49 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19">
-        <v>238</v>
+        <v>432</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F19">
-        <v>238</v>
+        <v>432</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M19">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P19" t="s">
         <v>33</v>
       </c>
       <c r="Q19">
-        <v>2350000</v>
+        <v>1758600</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1656,49 +1650,49 @@
         <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="E20" t="s">
         <v>62</v>
       </c>
       <c r="F20">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="G20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M20">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
       <c r="O20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P20" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="Q20">
-        <v>4687500</v>
+        <v>2350000</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1709,99 +1703,99 @@
         <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
         <v>62</v>
       </c>
       <c r="F21">
-        <v>218.5</v>
+        <v>125</v>
       </c>
       <c r="G21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M21">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N21">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q21">
-        <v>3000000</v>
+        <v>4687500</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22">
         <v>230</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F22">
-        <v>11.5</v>
+        <v>218.5</v>
       </c>
       <c r="G22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M22">
         <v>11500</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="O22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q22">
         <v>3000000</v>
@@ -1815,49 +1809,49 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23">
-        <v>129</v>
+        <v>230</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F23">
-        <v>129</v>
+        <v>11.5</v>
       </c>
       <c r="G23" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" t="s">
+        <v>67</v>
+      </c>
+      <c r="K23" t="s">
         <v>69</v>
       </c>
-      <c r="H23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" t="s">
-        <v>69</v>
-      </c>
-      <c r="J23" t="s">
-        <v>69</v>
-      </c>
-      <c r="K23" t="s">
-        <v>70</v>
-      </c>
       <c r="L23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M23">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q23">
-        <v>4837500</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1868,34 +1862,34 @@
         <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D24">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F24">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M24">
         <v>2000</v>
@@ -1904,18 +1898,18 @@
         <v>100</v>
       </c>
       <c r="O24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P24" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q24">
-        <v>4500000</v>
+        <v>4837500</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
         <v>52</v>
@@ -1924,46 +1918,46 @@
         <v>54</v>
       </c>
       <c r="D25">
-        <v>140</v>
+        <v>700.0000199999999</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F25">
-        <v>140</v>
+        <v>350.00001</v>
       </c>
       <c r="G25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K25" t="s">
         <v>70</v>
       </c>
       <c r="L25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M25">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O25" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P25" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q25">
-        <v>5250000</v>
+        <v>32666668</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1971,37 +1965,37 @@
         <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26">
         <v>700.0000199999999</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F26">
         <v>350.00001</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M26">
         <v>3000</v>
@@ -2010,65 +2004,12 @@
         <v>50</v>
       </c>
       <c r="O26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q26">
-        <v>32666668</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27">
-        <v>700.0000199999999</v>
-      </c>
-      <c r="E27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27">
-        <v>350.00001</v>
-      </c>
-      <c r="G27" t="s">
-        <v>69</v>
-      </c>
-      <c r="H27" t="s">
-        <v>69</v>
-      </c>
-      <c r="I27" t="s">
-        <v>69</v>
-      </c>
-      <c r="J27" t="s">
-        <v>69</v>
-      </c>
-      <c r="K27" t="s">
-        <v>72</v>
-      </c>
-      <c r="L27" t="s">
-        <v>69</v>
-      </c>
-      <c r="M27">
-        <v>3000</v>
-      </c>
-      <c r="N27">
-        <v>50</v>
-      </c>
-      <c r="O27" t="s">
-        <v>82</v>
-      </c>
-      <c r="P27" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q27">
         <v>32666668</v>
       </c>
     </row>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="87">
   <si>
     <t>상장일</t>
   </si>
@@ -67,6 +67,9 @@
     <t>총기관배정수량</t>
   </si>
   <si>
+    <t>2024-08-21</t>
+  </si>
+  <si>
     <t>2024-08-19</t>
   </si>
   <si>
@@ -115,6 +118,9 @@
     <t>2024-06-28</t>
   </si>
   <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
     <t>전진건설로봇</t>
   </si>
   <si>
@@ -166,10 +172,13 @@
     <t>에이치브이엠</t>
   </si>
   <si>
+    <t>코스닥</t>
+  </si>
+  <si>
     <t>코스피</t>
   </si>
   <si>
-    <t>코스닥</t>
+    <t>한국</t>
   </si>
   <si>
     <t>미래</t>
@@ -178,9 +187,6 @@
     <t>하나</t>
   </si>
   <si>
-    <t>한국</t>
-  </si>
-  <si>
     <t>키움</t>
   </si>
   <si>
@@ -217,6 +223,9 @@
     <t>인수</t>
   </si>
   <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -244,7 +253,7 @@
     <t>2024-06-19</t>
   </si>
   <si>
-    <t>2024-08-09</t>
+    <t>2024-08-14</t>
   </si>
   <si>
     <t>2024-07-30</t>
@@ -623,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -684,52 +693,52 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M2">
-        <v>16500</v>
+        <v>13000</v>
       </c>
       <c r="N2">
         <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="Q2">
-        <v>2078175</v>
+        <v>723700</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -737,105 +746,105 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M3">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="N3">
         <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q3">
-        <v>1050000</v>
+        <v>2078175</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M4">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P4" t="s">
         <v>21</v>
       </c>
       <c r="Q4">
-        <v>720000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -843,52 +852,52 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F5">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M5">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5" t="s">
+        <v>71</v>
+      </c>
+      <c r="P5" t="s">
         <v>22</v>
       </c>
-      <c r="P5" t="s">
-        <v>76</v>
-      </c>
       <c r="Q5">
-        <v>540250</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -896,52 +905,52 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F6">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" t="s">
         <v>69</v>
       </c>
-      <c r="P6" t="s">
-        <v>22</v>
-      </c>
       <c r="Q6">
-        <v>4350000</v>
+        <v>540250</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -949,52 +958,52 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F7">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M7">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q7">
-        <v>1050000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1002,52 +1011,52 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M8">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="Q8">
-        <v>1675500</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1055,52 +1064,52 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F9">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M9">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="Q9">
-        <v>1012500</v>
+        <v>1675500</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1108,102 +1117,102 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>2660</v>
+        <v>297</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F10">
-        <v>2553.6</v>
+        <v>297</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M10">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="N10">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P10" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>9340690</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>2660</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F11">
-        <v>106.4</v>
+        <v>2553.6</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M11">
         <v>35000</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q11">
         <v>9340690</v>
@@ -1214,52 +1223,52 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12">
-        <v>120</v>
+        <v>2660</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12">
-        <v>120</v>
+        <v>106.4</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M12">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q12">
-        <v>4500000</v>
+        <v>9340690</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1267,37 +1276,37 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M13">
         <v>2000</v>
@@ -1306,13 +1315,13 @@
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="P13" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="Q13">
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1320,52 +1329,52 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F14">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M14">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q14">
-        <v>1187900</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1373,90 +1382,90 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15">
-        <v>4350</v>
+        <v>161.8</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F15">
-        <v>1435.5</v>
+        <v>161.8</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M15">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="N15">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="O15" t="s">
         <v>31</v>
       </c>
       <c r="P15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q15">
-        <v>21750000</v>
+        <v>1187900</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16">
         <v>4350</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F16">
         <v>1435.5</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M16">
         <v>60000</v>
@@ -1465,10 +1474,10 @@
         <v>33</v>
       </c>
       <c r="O16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q16">
         <v>21750000</v>
@@ -1476,52 +1485,52 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D17">
         <v>4350</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F17">
-        <v>1305</v>
+        <v>1435.5</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M17">
         <v>60000</v>
       </c>
       <c r="N17">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q17">
         <v>21750000</v>
@@ -1529,52 +1538,52 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D18">
         <v>4350</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F18">
-        <v>174</v>
+        <v>1305</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M18">
         <v>60000</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q18">
         <v>21750000</v>
@@ -1585,52 +1594,52 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D19">
-        <v>80</v>
+        <v>4350</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F19">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M19">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q19">
-        <v>3000000</v>
+        <v>21750000</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1638,52 +1647,52 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20">
-        <v>289.6</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F20">
-        <v>289.6</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M20">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
       <c r="O20" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="P20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q20">
-        <v>1357500</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1691,102 +1700,102 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D21">
-        <v>575.89</v>
+        <v>289.6</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F21">
-        <v>541.3366</v>
+        <v>289.6</v>
       </c>
       <c r="G21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M21">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N21">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q21">
-        <v>1906400</v>
+        <v>1357500</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D22">
         <v>575.89</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F22">
-        <v>34.5534</v>
+        <v>541.3366</v>
       </c>
       <c r="G22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M22">
         <v>43300</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="O22" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="P22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q22">
         <v>1906400</v>
@@ -1797,51 +1806,104 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23">
+        <v>575.89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23">
+        <v>34.5534</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" t="s">
+        <v>66</v>
+      </c>
+      <c r="K23" t="s">
+        <v>68</v>
+      </c>
+      <c r="L23" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23">
+        <v>43300</v>
+      </c>
+      <c r="N23">
+        <v>6</v>
+      </c>
+      <c r="O23" t="s">
+        <v>77</v>
+      </c>
+      <c r="P23" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q23">
+        <v>1906400</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
         <v>51</v>
       </c>
-      <c r="D23">
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24">
         <v>432</v>
       </c>
-      <c r="E23" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23">
+      <c r="E24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24">
         <v>432</v>
       </c>
-      <c r="G23" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" t="s">
-        <v>64</v>
-      </c>
-      <c r="K23" t="s">
-        <v>65</v>
-      </c>
-      <c r="L23" t="s">
-        <v>64</v>
-      </c>
-      <c r="M23">
+      <c r="G24" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" t="s">
+        <v>66</v>
+      </c>
+      <c r="K24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24">
         <v>18000</v>
       </c>
-      <c r="N23">
+      <c r="N24">
         <v>100</v>
       </c>
-      <c r="O23" t="s">
-        <v>75</v>
-      </c>
-      <c r="P23" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q23">
+      <c r="O24" t="s">
+        <v>78</v>
+      </c>
+      <c r="P24" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q24">
         <v>1758600</v>
       </c>
     </row>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>상장일</t>
   </si>
@@ -67,6 +67,9 @@
     <t>총기관배정수량</t>
   </si>
   <si>
+    <t>2024-08-22</t>
+  </si>
+  <si>
     <t>2024-08-21</t>
   </si>
   <si>
@@ -118,9 +121,15 @@
     <t>2024-06-28</t>
   </si>
   <si>
+    <t>M83</t>
+  </si>
+  <si>
     <t>티디에스팜</t>
   </si>
   <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
     <t>전진건설로봇</t>
   </si>
   <si>
@@ -178,9 +187,18 @@
     <t>코스피</t>
   </si>
   <si>
+    <t>신영</t>
+  </si>
+  <si>
+    <t>유진</t>
+  </si>
+  <si>
     <t>한국</t>
   </si>
   <si>
+    <t>대신</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
@@ -200,9 +218,6 @@
   </si>
   <si>
     <t>SK</t>
-  </si>
-  <si>
-    <t>대신</t>
   </si>
   <si>
     <t>제이피모간회사</t>
@@ -632,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -693,847 +708,847 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F2">
-        <v>130</v>
+        <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M2">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="N2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O2" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="P2" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="Q2">
-        <v>723700</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3">
-        <v>507.81225</v>
+        <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F3">
-        <v>507.81225</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M3">
-        <v>16500</v>
+        <v>16000</v>
       </c>
       <c r="N3">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="P3" t="s">
         <v>21</v>
       </c>
       <c r="Q3">
-        <v>2078175</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F4">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M4">
-        <v>15500</v>
+        <v>13000</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P4" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="Q4">
-        <v>1050000</v>
+        <v>723700</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D5">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F5">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M5">
-        <v>29000</v>
+        <v>2000</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P5" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="Q5">
-        <v>720000</v>
+        <v>4875000</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>157.71</v>
+        <v>507.81225</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F6">
-        <v>157.71</v>
+        <v>507.81225</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M6">
-        <v>21000</v>
+        <v>16500</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="P6" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="Q6">
-        <v>540250</v>
+        <v>2078175</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D7">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F7">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M7">
-        <v>2000</v>
+        <v>15500</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q7">
-        <v>4350000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F8">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M8">
-        <v>16000</v>
+        <v>29000</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P8" t="s">
         <v>23</v>
       </c>
       <c r="Q8">
-        <v>1050000</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>223.4</v>
+        <v>157.71</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F9">
-        <v>223.4</v>
+        <v>157.71</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M9">
-        <v>10000</v>
+        <v>21000</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P9" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>1675500</v>
+        <v>540250</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>297</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F10">
-        <v>297</v>
+        <v>116</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M10">
-        <v>22000</v>
+        <v>2000</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q10">
-        <v>1012500</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>2660</v>
+        <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F11">
-        <v>2553.6</v>
+        <v>224</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M11">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="N11">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="P11" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="Q11">
-        <v>9340690</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D12">
-        <v>2660</v>
+        <v>223.4</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F12">
-        <v>106.4</v>
+        <v>223.4</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M12">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="P12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q12">
-        <v>9340690</v>
+        <v>1675500</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>297</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F13">
-        <v>120</v>
+        <v>297</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P13" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="Q13">
-        <v>4500000</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D14">
-        <v>80</v>
+        <v>2660</v>
       </c>
       <c r="E14" t="s">
         <v>61</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>2553.6</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M14">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O14" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="P14" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="Q14">
-        <v>3000000</v>
+        <v>9340690</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
         <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D15">
-        <v>161.8</v>
+        <v>2660</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F15">
-        <v>161.8</v>
+        <v>106.4</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K15" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M15">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O15" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="P15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q15">
-        <v>1187900</v>
+        <v>9340690</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16">
-        <v>4350</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F16">
-        <v>1435.5</v>
+        <v>120</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M16">
-        <v>60000</v>
+        <v>2000</v>
       </c>
       <c r="N16">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="P16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q16">
-        <v>21750000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17" t="s">
+        <v>72</v>
+      </c>
+      <c r="L17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17">
+        <v>2000</v>
+      </c>
+      <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17" t="s">
         <v>29</v>
       </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17">
-        <v>4350</v>
-      </c>
-      <c r="E17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17">
-        <v>1435.5</v>
-      </c>
-      <c r="G17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" t="s">
-        <v>66</v>
-      </c>
-      <c r="K17" t="s">
-        <v>67</v>
-      </c>
-      <c r="L17" t="s">
-        <v>66</v>
-      </c>
-      <c r="M17">
-        <v>60000</v>
-      </c>
-      <c r="N17">
-        <v>33</v>
-      </c>
-      <c r="O17" t="s">
-        <v>32</v>
-      </c>
       <c r="P17" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="Q17">
-        <v>21750000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1541,102 +1556,102 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18">
-        <v>4350</v>
+        <v>161.8</v>
       </c>
       <c r="E18" t="s">
         <v>60</v>
       </c>
       <c r="F18">
-        <v>1305</v>
+        <v>161.8</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K18" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M18">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="N18">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O18" t="s">
         <v>32</v>
       </c>
       <c r="P18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q18">
-        <v>21750000</v>
+        <v>1187900</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D19">
         <v>4350</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F19">
-        <v>174</v>
+        <v>1435.5</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K19" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M19">
         <v>60000</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="O19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P19" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Q19">
         <v>21750000</v>
@@ -1647,263 +1662,422 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D20">
-        <v>80</v>
+        <v>4350</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F20">
-        <v>80</v>
+        <v>1435.5</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K20" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M20">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="O20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P20" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Q20">
-        <v>3000000</v>
+        <v>21750000</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D21">
-        <v>289.6</v>
+        <v>4350</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F21">
-        <v>289.6</v>
+        <v>1305</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K21" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M21">
-        <v>16000</v>
+        <v>60000</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="O21" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="P21" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="Q21">
-        <v>1357500</v>
+        <v>21750000</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D22">
-        <v>575.89</v>
+        <v>4350</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F22">
-        <v>541.3366</v>
+        <v>174</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K22" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M22">
-        <v>43300</v>
+        <v>60000</v>
       </c>
       <c r="N22">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="O22" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="P22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q22">
-        <v>1906400</v>
+        <v>21750000</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D23">
-        <v>575.89</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F23">
-        <v>34.5534</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K23" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M23">
-        <v>43300</v>
+        <v>2000</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="O23" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="P23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q23">
-        <v>1906400</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D24">
-        <v>432</v>
+        <v>289.6</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F24">
-        <v>432</v>
+        <v>289.6</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H24" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I24" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J24" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K24" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L24" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M24">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="Q24">
+        <v>1357500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>575.89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25">
+        <v>541.3366</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" t="s">
+        <v>71</v>
+      </c>
+      <c r="K25" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" t="s">
+        <v>71</v>
+      </c>
+      <c r="M25">
+        <v>43300</v>
+      </c>
+      <c r="N25">
+        <v>94</v>
+      </c>
+      <c r="O25" t="s">
+        <v>82</v>
+      </c>
+      <c r="P25" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q25">
+        <v>1906400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26">
+        <v>575.89</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26">
+        <v>34.5534</v>
+      </c>
+      <c r="G26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" t="s">
+        <v>71</v>
+      </c>
+      <c r="K26" t="s">
+        <v>73</v>
+      </c>
+      <c r="L26" t="s">
+        <v>71</v>
+      </c>
+      <c r="M26">
+        <v>43300</v>
+      </c>
+      <c r="N26">
+        <v>6</v>
+      </c>
+      <c r="O26" t="s">
+        <v>82</v>
+      </c>
+      <c r="P26" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q26">
+        <v>1906400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27">
+        <v>432</v>
+      </c>
+      <c r="E27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27">
+        <v>432</v>
+      </c>
+      <c r="G27" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" t="s">
+        <v>71</v>
+      </c>
+      <c r="J27" t="s">
+        <v>71</v>
+      </c>
+      <c r="K27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L27" t="s">
+        <v>71</v>
+      </c>
+      <c r="M27">
+        <v>18000</v>
+      </c>
+      <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27" t="s">
+        <v>83</v>
+      </c>
+      <c r="P27" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q27">
         <v>1758600</v>
       </c>
     </row>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="94">
   <si>
     <t>상장일</t>
   </si>
@@ -70,6 +70,9 @@
     <t>2024-08-22</t>
   </si>
   <si>
+    <t>2024-08-23</t>
+  </si>
+  <si>
     <t>2024-08-21</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>M83</t>
   </si>
   <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
     <t>티디에스팜</t>
   </si>
   <si>
@@ -193,6 +199,9 @@
     <t>유진</t>
   </si>
   <si>
+    <t>NH</t>
+  </si>
+  <si>
     <t>한국</t>
   </si>
   <si>
@@ -212,9 +221,6 @@
   </si>
   <si>
     <t>삼성</t>
-  </si>
-  <si>
-    <t>NH</t>
   </si>
   <si>
     <t>SK</t>
@@ -647,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -708,37 +714,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M2">
         <v>16000</v>
@@ -747,10 +753,10 @@
         <v>95</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q2">
         <v>2100000</v>
@@ -761,37 +767,37 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3">
         <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M3">
         <v>16000</v>
@@ -800,10 +806,10 @@
         <v>5</v>
       </c>
       <c r="O3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q3">
         <v>2100000</v>
@@ -814,158 +820,158 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F4">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M4">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="P4" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="Q4">
-        <v>723700</v>
+        <v>1156798</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5">
         <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F5">
         <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M5">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q5">
-        <v>4875000</v>
+        <v>723700</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M6">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P6" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="Q6">
-        <v>2078175</v>
+        <v>4875000</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -973,105 +979,105 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D7">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M7">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q7">
-        <v>1050000</v>
+        <v>2078175</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M8">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P8" t="s">
         <v>23</v>
       </c>
       <c r="Q8">
-        <v>720000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1079,52 +1085,52 @@
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M9">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9" t="s">
+        <v>78</v>
+      </c>
+      <c r="P9" t="s">
         <v>24</v>
       </c>
-      <c r="P9" t="s">
-        <v>74</v>
-      </c>
       <c r="Q9">
-        <v>540250</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1132,52 +1138,52 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M10">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="P10" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="Q10">
-        <v>4350000</v>
+        <v>540250</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1185,52 +1191,52 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F11">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M11">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q11">
-        <v>1050000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1238,52 +1244,52 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F12">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M12">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="P12" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="Q12">
-        <v>1675500</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1291,52 +1297,52 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F13">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M13">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="Q13">
-        <v>1012500</v>
+        <v>1675500</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1344,102 +1350,102 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14">
-        <v>2660</v>
+        <v>297</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F14">
-        <v>2553.6</v>
+        <v>297</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M14">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="N14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P14" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="Q14">
-        <v>9340690</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15">
         <v>2660</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15">
-        <v>106.4</v>
+        <v>2553.6</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M15">
         <v>35000</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="O15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q15">
         <v>9340690</v>
@@ -1450,52 +1456,52 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D16">
-        <v>120</v>
+        <v>2660</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F16">
-        <v>120</v>
+        <v>106.4</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M16">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q16">
-        <v>4500000</v>
+        <v>9340690</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1503,37 +1509,37 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F17">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M17">
         <v>2000</v>
@@ -1542,13 +1548,13 @@
         <v>100</v>
       </c>
       <c r="O17" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="Q17">
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1556,52 +1562,52 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F18">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M18">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="Q18">
-        <v>1187900</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1609,90 +1615,90 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19">
-        <v>4350</v>
+        <v>161.8</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F19">
-        <v>1435.5</v>
+        <v>161.8</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M19">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="N19">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="O19" t="s">
         <v>33</v>
       </c>
       <c r="P19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q19">
-        <v>21750000</v>
+        <v>1187900</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D20">
         <v>4350</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F20">
         <v>1435.5</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M20">
         <v>60000</v>
@@ -1701,10 +1707,10 @@
         <v>33</v>
       </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q20">
         <v>21750000</v>
@@ -1712,52 +1718,52 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D21">
         <v>4350</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F21">
-        <v>1305</v>
+        <v>1435.5</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M21">
         <v>60000</v>
       </c>
       <c r="N21">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q21">
         <v>21750000</v>
@@ -1765,52 +1771,52 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D22">
         <v>4350</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F22">
-        <v>174</v>
+        <v>1305</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M22">
         <v>60000</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q22">
         <v>21750000</v>
@@ -1821,52 +1827,52 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D23">
-        <v>80</v>
+        <v>4350</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F23">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M23">
-        <v>2000</v>
+        <v>60000</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q23">
-        <v>3000000</v>
+        <v>21750000</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1874,52 +1880,52 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24">
-        <v>289.6</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F24">
-        <v>289.6</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M24">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q24">
-        <v>1357500</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1927,102 +1933,102 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25">
-        <v>575.89</v>
+        <v>289.6</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F25">
-        <v>541.3366</v>
+        <v>289.6</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M25">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N25">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q25">
-        <v>1906400</v>
+        <v>1357500</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>575.89</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F26">
-        <v>34.5534</v>
+        <v>541.3366</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M26">
         <v>43300</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="O26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q26">
         <v>1906400</v>
@@ -2033,51 +2039,104 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D27">
+        <v>575.89</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27">
+        <v>34.5534</v>
+      </c>
+      <c r="G27" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" t="s">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" t="s">
+        <v>73</v>
+      </c>
+      <c r="M27">
+        <v>43300</v>
+      </c>
+      <c r="N27">
+        <v>6</v>
+      </c>
+      <c r="O27" t="s">
+        <v>84</v>
+      </c>
+      <c r="P27" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q27">
+        <v>1906400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28">
         <v>432</v>
       </c>
-      <c r="E27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27">
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28">
         <v>432</v>
       </c>
-      <c r="G27" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" t="s">
-        <v>71</v>
-      </c>
-      <c r="I27" t="s">
-        <v>71</v>
-      </c>
-      <c r="J27" t="s">
-        <v>71</v>
-      </c>
-      <c r="K27" t="s">
-        <v>72</v>
-      </c>
-      <c r="L27" t="s">
-        <v>71</v>
-      </c>
-      <c r="M27">
+      <c r="G28" t="s">
+        <v>73</v>
+      </c>
+      <c r="H28" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s">
+        <v>74</v>
+      </c>
+      <c r="L28" t="s">
+        <v>73</v>
+      </c>
+      <c r="M28">
         <v>18000</v>
       </c>
-      <c r="N27">
+      <c r="N28">
         <v>100</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O28" t="s">
+        <v>85</v>
+      </c>
+      <c r="P28" t="s">
         <v>83</v>
       </c>
-      <c r="P27" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q27">
+      <c r="Q28">
         <v>1758600</v>
       </c>
     </row>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="88">
   <si>
     <t>상장일</t>
   </si>
@@ -118,162 +118,147 @@
     <t>2024-07-03</t>
   </si>
   <si>
+    <t>M83</t>
+  </si>
+  <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
+    <t>케이쓰리아이</t>
+  </si>
+  <si>
+    <t>넥스트바이오메디컬</t>
+  </si>
+  <si>
+    <t>유라클</t>
+  </si>
+  <si>
+    <t>교보16호스팩</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
+    <t>아이빔테크놀로지</t>
+  </si>
+  <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
+    <t>SK증권제13호스팩</t>
+  </si>
+  <si>
+    <t>엑셀세라퓨틱스</t>
+  </si>
+  <si>
+    <t>시프트업</t>
+  </si>
+  <si>
+    <t>이베스트스팩6호</t>
+  </si>
+  <si>
+    <t>하스</t>
+  </si>
+  <si>
+    <t>코스닥</t>
+  </si>
+  <si>
+    <t>코스피</t>
+  </si>
+  <si>
+    <t>신영</t>
+  </si>
+  <si>
+    <t>유진</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>대신</t>
+  </si>
+  <si>
+    <t>미래</t>
+  </si>
+  <si>
+    <t>하나</t>
+  </si>
+  <si>
+    <t>키움</t>
+  </si>
+  <si>
+    <t>교보</t>
+  </si>
+  <si>
+    <t>삼성</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>제이피모간회사</t>
+  </si>
+  <si>
+    <t>신한</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>대표</t>
+  </si>
+  <si>
+    <t>인수</t>
+  </si>
+  <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
+    <t>2024-08-07</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
+    <t>2024-07-22</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
     <t>2024-07-02</t>
   </si>
   <si>
-    <t>2024-06-28</t>
-  </si>
-  <si>
-    <t>M83</t>
-  </si>
-  <si>
-    <t>이엔셀</t>
-  </si>
-  <si>
-    <t>티디에스팜</t>
-  </si>
-  <si>
-    <t>대신밸런스제18호스팩</t>
-  </si>
-  <si>
-    <t>전진건설로봇</t>
-  </si>
-  <si>
-    <t>케이쓰리아이</t>
-  </si>
-  <si>
-    <t>넥스트바이오메디컬</t>
-  </si>
-  <si>
-    <t>유라클</t>
-  </si>
-  <si>
-    <t>교보16호스팩</t>
-  </si>
-  <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
-    <t>아이빔테크놀로지</t>
-  </si>
-  <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
-    <t>시프트업</t>
-  </si>
-  <si>
-    <t>이베스트스팩6호</t>
-  </si>
-  <si>
-    <t>하스</t>
-  </si>
-  <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
-    <t>에이치브이엠</t>
-  </si>
-  <si>
-    <t>코스닥</t>
-  </si>
-  <si>
-    <t>코스피</t>
-  </si>
-  <si>
-    <t>신영</t>
-  </si>
-  <si>
-    <t>유진</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>한국</t>
-  </si>
-  <si>
-    <t>대신</t>
-  </si>
-  <si>
-    <t>미래</t>
-  </si>
-  <si>
-    <t>하나</t>
-  </si>
-  <si>
-    <t>키움</t>
-  </si>
-  <si>
-    <t>교보</t>
-  </si>
-  <si>
-    <t>삼성</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>제이피모간회사</t>
-  </si>
-  <si>
-    <t>신한</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>대표</t>
-  </si>
-  <si>
-    <t>인수</t>
-  </si>
-  <si>
-    <t>2024-08-09</t>
-  </si>
-  <si>
-    <t>2024-08-08</t>
-  </si>
-  <si>
-    <t>2024-08-07</t>
-  </si>
-  <si>
-    <t>2024-08-01</t>
-  </si>
-  <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
     <t>2024-06-24</t>
   </si>
   <si>
-    <t>2024-06-20</t>
-  </si>
-  <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
     <t>2024-08-14</t>
   </si>
   <si>
@@ -293,9 +278,6 @@
   </si>
   <si>
     <t>2024-06-27</t>
-  </si>
-  <si>
-    <t>2024-06-25</t>
   </si>
 </sst>
 </file>
@@ -653,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -714,37 +696,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D2">
         <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F2">
         <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M2">
         <v>16000</v>
@@ -767,37 +749,37 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D3">
         <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M3">
         <v>16000</v>
@@ -820,37 +802,37 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>239.7204</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F4">
         <v>239.7204</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M4">
         <v>15300</v>
@@ -873,37 +855,37 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F5">
         <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M5">
         <v>13000</v>
@@ -912,10 +894,10 @@
         <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="Q5">
         <v>723700</v>
@@ -926,37 +908,37 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F6">
         <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M6">
         <v>2000</v>
@@ -965,10 +947,10 @@
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="Q6">
         <v>4875000</v>
@@ -979,37 +961,37 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D7">
         <v>507.81225</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F7">
         <v>507.81225</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M7">
         <v>16500</v>
@@ -1018,7 +1000,7 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P7" t="s">
         <v>23</v>
@@ -1032,37 +1014,37 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F8">
         <v>217</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M8">
         <v>15500</v>
@@ -1071,7 +1053,7 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P8" t="s">
         <v>23</v>
@@ -1085,37 +1067,37 @@
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D9">
         <v>290</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9">
         <v>290</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M9">
         <v>29000</v>
@@ -1124,7 +1106,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P9" t="s">
         <v>24</v>
@@ -1138,37 +1120,37 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D10">
         <v>157.71</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F10">
         <v>157.71</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M10">
         <v>21000</v>
@@ -1180,7 +1162,7 @@
         <v>25</v>
       </c>
       <c r="P10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="Q10">
         <v>540250</v>
@@ -1191,37 +1173,37 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F11">
         <v>116</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M11">
         <v>2000</v>
@@ -1230,7 +1212,7 @@
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -1244,37 +1226,37 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D12">
         <v>224</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F12">
         <v>224</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M12">
         <v>16000</v>
@@ -1283,7 +1265,7 @@
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -1297,37 +1279,37 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>223.4</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F13">
         <v>223.4</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M13">
         <v>10000</v>
@@ -1339,7 +1321,7 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="Q13">
         <v>1675500</v>
@@ -1350,37 +1332,37 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14">
         <v>297</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F14">
         <v>297</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M14">
         <v>22000</v>
@@ -1389,7 +1371,7 @@
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P14" t="s">
         <v>29</v>
@@ -1403,37 +1385,37 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D15">
         <v>2660</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F15">
         <v>2553.6</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M15">
         <v>35000</v>
@@ -1442,10 +1424,10 @@
         <v>96</v>
       </c>
       <c r="O15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P15" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="Q15">
         <v>9340690</v>
@@ -1456,37 +1438,37 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D16">
         <v>2660</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F16">
         <v>106.4</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K16" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M16">
         <v>35000</v>
@@ -1495,10 +1477,10 @@
         <v>4</v>
       </c>
       <c r="O16" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="Q16">
         <v>9340690</v>
@@ -1509,37 +1491,37 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D17">
         <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F17">
         <v>120</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M17">
         <v>2000</v>
@@ -1548,10 +1530,10 @@
         <v>100</v>
       </c>
       <c r="O17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P17" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="Q17">
         <v>4500000</v>
@@ -1562,37 +1544,37 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18">
         <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F18">
         <v>80</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K18" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M18">
         <v>2000</v>
@@ -1604,7 +1586,7 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q18">
         <v>3000000</v>
@@ -1615,37 +1597,37 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D19">
         <v>161.8</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F19">
         <v>161.8</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M19">
         <v>10000</v>
@@ -1657,7 +1639,7 @@
         <v>33</v>
       </c>
       <c r="P19" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Q19">
         <v>1187900</v>
@@ -1668,37 +1650,37 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20">
         <v>4350</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F20">
         <v>1435.5</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K20" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M20">
         <v>60000</v>
@@ -1707,10 +1689,10 @@
         <v>33</v>
       </c>
       <c r="O20" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="P20" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q20">
         <v>21750000</v>
@@ -1721,37 +1703,37 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <v>4350</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F21">
         <v>1435.5</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K21" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M21">
         <v>60000</v>
@@ -1760,10 +1742,10 @@
         <v>33</v>
       </c>
       <c r="O21" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="P21" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q21">
         <v>21750000</v>
@@ -1774,37 +1756,37 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D22">
         <v>4350</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F22">
         <v>1305</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M22">
         <v>60000</v>
@@ -1813,10 +1795,10 @@
         <v>30</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="P22" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q22">
         <v>21750000</v>
@@ -1827,37 +1809,37 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D23">
         <v>4350</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F23">
         <v>174</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K23" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M23">
         <v>60000</v>
@@ -1866,10 +1848,10 @@
         <v>4</v>
       </c>
       <c r="O23" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="P23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q23">
         <v>21750000</v>
@@ -1880,37 +1862,37 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
         <v>53</v>
-      </c>
-      <c r="C24" t="s">
-        <v>57</v>
       </c>
       <c r="D24">
         <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F24">
         <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K24" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M24">
         <v>2000</v>
@@ -1919,10 +1901,10 @@
         <v>100</v>
       </c>
       <c r="O24" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="P24" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q24">
         <v>3000000</v>
@@ -1933,37 +1915,37 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D25">
         <v>289.6</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F25">
         <v>289.6</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K25" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M25">
         <v>16000</v>
@@ -1972,172 +1954,13 @@
         <v>100</v>
       </c>
       <c r="O25" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Q25">
         <v>1357500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26">
-        <v>575.89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26">
-        <v>541.3366</v>
-      </c>
-      <c r="G26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H26" t="s">
-        <v>73</v>
-      </c>
-      <c r="I26" t="s">
-        <v>73</v>
-      </c>
-      <c r="J26" t="s">
-        <v>73</v>
-      </c>
-      <c r="K26" t="s">
-        <v>74</v>
-      </c>
-      <c r="L26" t="s">
-        <v>73</v>
-      </c>
-      <c r="M26">
-        <v>43300</v>
-      </c>
-      <c r="N26">
-        <v>94</v>
-      </c>
-      <c r="O26" t="s">
-        <v>84</v>
-      </c>
-      <c r="P26" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q26">
-        <v>1906400</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27">
-        <v>575.89</v>
-      </c>
-      <c r="E27" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27">
-        <v>34.5534</v>
-      </c>
-      <c r="G27" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" t="s">
-        <v>73</v>
-      </c>
-      <c r="I27" t="s">
-        <v>73</v>
-      </c>
-      <c r="J27" t="s">
-        <v>73</v>
-      </c>
-      <c r="K27" t="s">
-        <v>75</v>
-      </c>
-      <c r="L27" t="s">
-        <v>73</v>
-      </c>
-      <c r="M27">
-        <v>43300</v>
-      </c>
-      <c r="N27">
-        <v>6</v>
-      </c>
-      <c r="O27" t="s">
-        <v>84</v>
-      </c>
-      <c r="P27" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q27">
-        <v>1906400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28">
-        <v>432</v>
-      </c>
-      <c r="E28" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28">
-        <v>432</v>
-      </c>
-      <c r="G28" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" t="s">
-        <v>73</v>
-      </c>
-      <c r="I28" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28" t="s">
-        <v>73</v>
-      </c>
-      <c r="K28" t="s">
-        <v>74</v>
-      </c>
-      <c r="L28" t="s">
-        <v>73</v>
-      </c>
-      <c r="M28">
-        <v>18000</v>
-      </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
-      <c r="O28" t="s">
-        <v>85</v>
-      </c>
-      <c r="P28" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q28">
-        <v>1758600</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="85">
   <si>
     <t>상장일</t>
   </si>
@@ -115,150 +115,144 @@
     <t>2024-07-12</t>
   </si>
   <si>
+    <t>M83</t>
+  </si>
+  <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
+    <t>케이쓰리아이</t>
+  </si>
+  <si>
+    <t>넥스트바이오메디컬</t>
+  </si>
+  <si>
+    <t>유라클</t>
+  </si>
+  <si>
+    <t>교보16호스팩</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
+    <t>아이빔테크놀로지</t>
+  </si>
+  <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
+    <t>SK증권제13호스팩</t>
+  </si>
+  <si>
+    <t>엑셀세라퓨틱스</t>
+  </si>
+  <si>
+    <t>시프트업</t>
+  </si>
+  <si>
+    <t>이베스트스팩6호</t>
+  </si>
+  <si>
+    <t>코스닥</t>
+  </si>
+  <si>
+    <t>코스피</t>
+  </si>
+  <si>
+    <t>신영</t>
+  </si>
+  <si>
+    <t>유진</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>대신</t>
+  </si>
+  <si>
+    <t>미래</t>
+  </si>
+  <si>
+    <t>하나</t>
+  </si>
+  <si>
+    <t>키움</t>
+  </si>
+  <si>
+    <t>교보</t>
+  </si>
+  <si>
+    <t>삼성</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>제이피모간회사</t>
+  </si>
+  <si>
+    <t>신한</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>대표</t>
+  </si>
+  <si>
+    <t>인수</t>
+  </si>
+  <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
+    <t>2024-08-07</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
+    <t>2024-07-22</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
     <t>2024-07-03</t>
   </si>
   <si>
-    <t>M83</t>
-  </si>
-  <si>
-    <t>이엔셀</t>
-  </si>
-  <si>
-    <t>티디에스팜</t>
-  </si>
-  <si>
-    <t>대신밸런스제18호스팩</t>
-  </si>
-  <si>
-    <t>전진건설로봇</t>
-  </si>
-  <si>
-    <t>케이쓰리아이</t>
-  </si>
-  <si>
-    <t>넥스트바이오메디컬</t>
-  </si>
-  <si>
-    <t>유라클</t>
-  </si>
-  <si>
-    <t>교보16호스팩</t>
-  </si>
-  <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
-    <t>아이빔테크놀로지</t>
-  </si>
-  <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
-    <t>시프트업</t>
-  </si>
-  <si>
-    <t>이베스트스팩6호</t>
-  </si>
-  <si>
-    <t>하스</t>
-  </si>
-  <si>
-    <t>코스닥</t>
-  </si>
-  <si>
-    <t>코스피</t>
-  </si>
-  <si>
-    <t>신영</t>
-  </si>
-  <si>
-    <t>유진</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>한국</t>
-  </si>
-  <si>
-    <t>대신</t>
-  </si>
-  <si>
-    <t>미래</t>
-  </si>
-  <si>
-    <t>하나</t>
-  </si>
-  <si>
-    <t>키움</t>
-  </si>
-  <si>
-    <t>교보</t>
-  </si>
-  <si>
-    <t>삼성</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>제이피모간회사</t>
-  </si>
-  <si>
-    <t>신한</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>대표</t>
-  </si>
-  <si>
-    <t>인수</t>
-  </si>
-  <si>
-    <t>2024-08-09</t>
-  </si>
-  <si>
-    <t>2024-08-08</t>
-  </si>
-  <si>
-    <t>2024-08-07</t>
-  </si>
-  <si>
-    <t>2024-08-01</t>
-  </si>
-  <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
     <t>2024-07-02</t>
   </si>
   <si>
-    <t>2024-06-24</t>
-  </si>
-  <si>
     <t>2024-08-14</t>
   </si>
   <si>
@@ -275,9 +269,6 @@
   </si>
   <si>
     <t>2024-07-05</t>
-  </si>
-  <si>
-    <t>2024-06-27</t>
   </si>
 </sst>
 </file>
@@ -635,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -696,37 +687,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M2">
         <v>16000</v>
@@ -749,37 +740,37 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3">
         <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
       <c r="G3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
         <v>69</v>
       </c>
-      <c r="H3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K3" t="s">
-        <v>71</v>
-      </c>
       <c r="L3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M3">
         <v>16000</v>
@@ -802,37 +793,37 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4">
         <v>239.7204</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4">
         <v>239.7204</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M4">
         <v>15300</v>
@@ -855,37 +846,37 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F5">
         <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M5">
         <v>13000</v>
@@ -894,10 +885,10 @@
         <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q5">
         <v>723700</v>
@@ -908,37 +899,37 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6">
         <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6">
         <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M6">
         <v>2000</v>
@@ -947,10 +938,10 @@
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q6">
         <v>4875000</v>
@@ -961,37 +952,37 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>507.81225</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F7">
         <v>507.81225</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M7">
         <v>16500</v>
@@ -1000,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
         <v>23</v>
@@ -1014,37 +1005,37 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F8">
         <v>217</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M8">
         <v>15500</v>
@@ -1053,7 +1044,7 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
         <v>23</v>
@@ -1067,37 +1058,37 @@
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9">
         <v>290</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9">
         <v>290</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M9">
         <v>29000</v>
@@ -1106,7 +1097,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P9" t="s">
         <v>24</v>
@@ -1120,37 +1111,37 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <v>157.71</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F10">
         <v>157.71</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M10">
         <v>21000</v>
@@ -1162,7 +1153,7 @@
         <v>25</v>
       </c>
       <c r="P10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q10">
         <v>540250</v>
@@ -1173,37 +1164,37 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F11">
         <v>116</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M11">
         <v>2000</v>
@@ -1212,7 +1203,7 @@
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -1226,37 +1217,37 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12">
         <v>224</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F12">
         <v>224</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M12">
         <v>16000</v>
@@ -1265,7 +1256,7 @@
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -1279,37 +1270,37 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13">
         <v>223.4</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F13">
         <v>223.4</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M13">
         <v>10000</v>
@@ -1321,7 +1312,7 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Q13">
         <v>1675500</v>
@@ -1332,37 +1323,37 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14">
         <v>297</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F14">
         <v>297</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M14">
         <v>22000</v>
@@ -1371,7 +1362,7 @@
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P14" t="s">
         <v>29</v>
@@ -1385,37 +1376,37 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15">
         <v>2660</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F15">
         <v>2553.6</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M15">
         <v>35000</v>
@@ -1424,10 +1415,10 @@
         <v>96</v>
       </c>
       <c r="O15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q15">
         <v>9340690</v>
@@ -1438,37 +1429,37 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16">
         <v>2660</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F16">
         <v>106.4</v>
       </c>
       <c r="G16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" t="s">
         <v>69</v>
       </c>
-      <c r="H16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" t="s">
-        <v>69</v>
-      </c>
-      <c r="J16" t="s">
-        <v>69</v>
-      </c>
-      <c r="K16" t="s">
-        <v>71</v>
-      </c>
       <c r="L16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M16">
         <v>35000</v>
@@ -1477,10 +1468,10 @@
         <v>4</v>
       </c>
       <c r="O16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q16">
         <v>9340690</v>
@@ -1491,37 +1482,37 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17">
         <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F17">
         <v>120</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M17">
         <v>2000</v>
@@ -1530,10 +1521,10 @@
         <v>100</v>
       </c>
       <c r="O17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q17">
         <v>4500000</v>
@@ -1544,37 +1535,37 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D18">
         <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F18">
         <v>80</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M18">
         <v>2000</v>
@@ -1586,7 +1577,7 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q18">
         <v>3000000</v>
@@ -1597,37 +1588,37 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D19">
         <v>161.8</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F19">
         <v>161.8</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M19">
         <v>10000</v>
@@ -1636,10 +1627,10 @@
         <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="P19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q19">
         <v>1187900</v>
@@ -1650,37 +1641,37 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20">
         <v>4350</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20">
         <v>1435.5</v>
       </c>
       <c r="G20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M20">
         <v>60000</v>
@@ -1689,10 +1680,10 @@
         <v>33</v>
       </c>
       <c r="O20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q20">
         <v>21750000</v>
@@ -1703,37 +1694,37 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D21">
         <v>4350</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F21">
         <v>1435.5</v>
       </c>
       <c r="G21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M21">
         <v>60000</v>
@@ -1742,10 +1733,10 @@
         <v>33</v>
       </c>
       <c r="O21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q21">
         <v>21750000</v>
@@ -1756,37 +1747,37 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D22">
         <v>4350</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F22">
         <v>1305</v>
       </c>
       <c r="G22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M22">
         <v>60000</v>
@@ -1795,10 +1786,10 @@
         <v>30</v>
       </c>
       <c r="O22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q22">
         <v>21750000</v>
@@ -1809,37 +1800,37 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>4350</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F23">
         <v>174</v>
       </c>
       <c r="G23" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" t="s">
+        <v>67</v>
+      </c>
+      <c r="K23" t="s">
         <v>69</v>
       </c>
-      <c r="H23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" t="s">
-        <v>69</v>
-      </c>
-      <c r="J23" t="s">
-        <v>69</v>
-      </c>
-      <c r="K23" t="s">
-        <v>71</v>
-      </c>
       <c r="L23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M23">
         <v>60000</v>
@@ -1848,10 +1839,10 @@
         <v>4</v>
       </c>
       <c r="O23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q23">
         <v>21750000</v>
@@ -1862,37 +1853,37 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
         <v>51</v>
-      </c>
-      <c r="C24" t="s">
-        <v>53</v>
       </c>
       <c r="D24">
         <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F24">
         <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M24">
         <v>2000</v>
@@ -1901,66 +1892,13 @@
         <v>100</v>
       </c>
       <c r="O24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q24">
         <v>3000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25">
-        <v>289.6</v>
-      </c>
-      <c r="E25" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25">
-        <v>289.6</v>
-      </c>
-      <c r="G25" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" t="s">
-        <v>69</v>
-      </c>
-      <c r="J25" t="s">
-        <v>69</v>
-      </c>
-      <c r="K25" t="s">
-        <v>70</v>
-      </c>
-      <c r="L25" t="s">
-        <v>69</v>
-      </c>
-      <c r="M25">
-        <v>16000</v>
-      </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25" t="s">
-        <v>80</v>
-      </c>
-      <c r="P25" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q25">
-        <v>1357500</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="88">
   <si>
     <t>상장일</t>
   </si>
@@ -67,6 +67,9 @@
     <t>총기관배정수량</t>
   </si>
   <si>
+    <t>2024-08-30</t>
+  </si>
+  <si>
     <t>2024-08-22</t>
   </si>
   <si>
@@ -115,6 +118,9 @@
     <t>2024-07-12</t>
   </si>
   <si>
+    <t>아이스크림미디어</t>
+  </si>
+  <si>
     <t>M83</t>
   </si>
   <si>
@@ -175,6 +181,9 @@
     <t>코스피</t>
   </si>
   <si>
+    <t>삼성</t>
+  </si>
+  <si>
     <t>신영</t>
   </si>
   <si>
@@ -202,9 +211,6 @@
     <t>교보</t>
   </si>
   <si>
-    <t>삼성</t>
-  </si>
-  <si>
     <t>SK</t>
   </si>
   <si>
@@ -251,6 +257,9 @@
   </si>
   <si>
     <t>2024-07-02</t>
+  </si>
+  <si>
+    <t>2024-08-26</t>
   </si>
   <si>
     <t>2024-08-14</t>
@@ -626,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -687,102 +696,102 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>240</v>
+        <v>787.2</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F2">
-        <v>228</v>
+        <v>787.2</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M2">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="N2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P2" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="Q2">
-        <v>2100000</v>
+        <v>1722000</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3">
         <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M3">
         <v>16000</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q3">
         <v>2100000</v>
@@ -793,52 +802,52 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4">
-        <v>239.7204</v>
+        <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F4">
-        <v>239.7204</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M4">
-        <v>15300</v>
+        <v>16000</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q4">
-        <v>1156798</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -846,158 +855,158 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M5">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="P5" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="Q5">
-        <v>723700</v>
+        <v>1156798</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F6">
         <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q6">
-        <v>4875000</v>
+        <v>723700</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F7">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M7">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="Q7">
-        <v>2078175</v>
+        <v>4875000</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1005,105 +1014,105 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F8">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M8">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q8">
-        <v>1050000</v>
+        <v>2078175</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M9">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P9" t="s">
         <v>24</v>
       </c>
       <c r="Q9">
-        <v>720000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1111,52 +1120,52 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M10">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" t="s">
         <v>25</v>
       </c>
-      <c r="P10" t="s">
-        <v>70</v>
-      </c>
       <c r="Q10">
-        <v>540250</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1164,52 +1173,52 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F11">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M11">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="Q11">
-        <v>4350000</v>
+        <v>540250</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1217,52 +1226,52 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F12">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M12">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q12">
-        <v>1050000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1270,52 +1279,52 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F13">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M13">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="P13" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="Q13">
-        <v>1675500</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1323,52 +1332,52 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F14">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="G14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M14">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="Q14">
-        <v>1012500</v>
+        <v>1675500</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1376,102 +1385,102 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15">
-        <v>2660</v>
+        <v>297</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F15">
-        <v>2553.6</v>
+        <v>297</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M15">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="N15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P15" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="Q15">
-        <v>9340690</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16">
         <v>2660</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F16">
-        <v>106.4</v>
+        <v>2553.6</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M16">
         <v>35000</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="O16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q16">
         <v>9340690</v>
@@ -1482,52 +1491,52 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17">
-        <v>120</v>
+        <v>2660</v>
       </c>
       <c r="E17" t="s">
         <v>55</v>
       </c>
       <c r="F17">
-        <v>120</v>
+        <v>106.4</v>
       </c>
       <c r="G17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M17">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q17">
-        <v>4500000</v>
+        <v>9340690</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1535,37 +1544,37 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D18">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F18">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M18">
         <v>2000</v>
@@ -1574,13 +1583,13 @@
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="P18" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q18">
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1588,52 +1597,52 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D19">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F19">
-        <v>161.8</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M19">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" t="s">
         <v>77</v>
       </c>
-      <c r="P19" t="s">
-        <v>83</v>
-      </c>
       <c r="Q19">
-        <v>1187900</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1641,90 +1650,90 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D20">
-        <v>4350</v>
+        <v>161.8</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F20">
-        <v>1435.5</v>
+        <v>161.8</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M20">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="N20">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="O20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q20">
-        <v>21750000</v>
+        <v>1187900</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <v>4350</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F21">
         <v>1435.5</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M21">
         <v>60000</v>
@@ -1733,10 +1742,10 @@
         <v>33</v>
       </c>
       <c r="O21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q21">
         <v>21750000</v>
@@ -1744,52 +1753,52 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D22">
         <v>4350</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F22">
-        <v>1305</v>
+        <v>1435.5</v>
       </c>
       <c r="G22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M22">
         <v>60000</v>
       </c>
       <c r="N22">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q22">
         <v>21750000</v>
@@ -1797,52 +1806,52 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D23">
         <v>4350</v>
       </c>
       <c r="E23" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F23">
-        <v>174</v>
+        <v>1305</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M23">
         <v>60000</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q23">
         <v>21750000</v>
@@ -1853,51 +1862,104 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D24">
+        <v>4350</v>
+      </c>
+      <c r="E24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24">
+        <v>174</v>
+      </c>
+      <c r="G24" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" t="s">
+        <v>69</v>
+      </c>
+      <c r="I24" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" t="s">
+        <v>69</v>
+      </c>
+      <c r="K24" t="s">
+        <v>71</v>
+      </c>
+      <c r="L24" t="s">
+        <v>69</v>
+      </c>
+      <c r="M24">
+        <v>60000</v>
+      </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
+      <c r="O24" t="s">
         <v>80</v>
       </c>
-      <c r="E24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24">
+      <c r="P24" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q24">
+        <v>21750000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25">
         <v>80</v>
       </c>
-      <c r="G24" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" t="s">
-        <v>67</v>
-      </c>
-      <c r="I24" t="s">
-        <v>67</v>
-      </c>
-      <c r="J24" t="s">
-        <v>67</v>
-      </c>
-      <c r="K24" t="s">
+      <c r="E25" t="s">
         <v>68</v>
       </c>
-      <c r="L24" t="s">
-        <v>67</v>
-      </c>
-      <c r="M24">
+      <c r="F25">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" t="s">
+        <v>69</v>
+      </c>
+      <c r="J25" t="s">
+        <v>69</v>
+      </c>
+      <c r="K25" t="s">
+        <v>70</v>
+      </c>
+      <c r="L25" t="s">
+        <v>69</v>
+      </c>
+      <c r="M25">
         <v>2000</v>
       </c>
-      <c r="N24">
+      <c r="N25">
         <v>100</v>
       </c>
-      <c r="O24" t="s">
-        <v>78</v>
-      </c>
-      <c r="P24" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q24">
+      <c r="O25" t="s">
+        <v>80</v>
+      </c>
+      <c r="P25" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q25">
         <v>3000000</v>
       </c>
     </row>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
   <si>
     <t>상장일</t>
   </si>
@@ -112,12 +112,6 @@
     <t>2024-07-15</t>
   </si>
   <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
     <t>아이스크림미디어</t>
   </si>
   <si>
@@ -169,12 +163,6 @@
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
-    <t>시프트업</t>
-  </si>
-  <si>
-    <t>이베스트스팩6호</t>
-  </si>
-  <si>
     <t>코스닥</t>
   </si>
   <si>
@@ -214,15 +202,6 @@
     <t>SK</t>
   </si>
   <si>
-    <t>제이피모간회사</t>
-  </si>
-  <si>
-    <t>신한</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -256,9 +235,6 @@
     <t>2024-07-03</t>
   </si>
   <si>
-    <t>2024-07-02</t>
-  </si>
-  <si>
     <t>2024-08-26</t>
   </si>
   <si>
@@ -275,9 +251,6 @@
   </si>
   <si>
     <t>2024-07-08</t>
-  </si>
-  <si>
-    <t>2024-07-05</t>
   </si>
 </sst>
 </file>
@@ -635,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -696,37 +669,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D2">
         <v>787.2</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F2">
         <v>787.2</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M2">
         <v>32000</v>
@@ -738,7 +711,7 @@
         <v>20</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="Q2">
         <v>1722000</v>
@@ -749,37 +722,37 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D3">
         <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>228</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M3">
         <v>16000</v>
@@ -802,37 +775,37 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D4">
         <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F4">
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M4">
         <v>16000</v>
@@ -855,37 +828,37 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D5">
         <v>239.7204</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>239.7204</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M5">
         <v>15300</v>
@@ -908,37 +881,37 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F6">
         <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M6">
         <v>13000</v>
@@ -947,10 +920,10 @@
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="Q6">
         <v>723700</v>
@@ -961,37 +934,37 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F7">
         <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M7">
         <v>2000</v>
@@ -1000,10 +973,10 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="P7" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="Q7">
         <v>4875000</v>
@@ -1014,37 +987,37 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>507.81225</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F8">
         <v>507.81225</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M8">
         <v>16500</v>
@@ -1053,7 +1026,7 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="P8" t="s">
         <v>24</v>
@@ -1067,37 +1040,37 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D9">
         <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9">
         <v>217</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M9">
         <v>15500</v>
@@ -1106,7 +1079,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="P9" t="s">
         <v>24</v>
@@ -1120,37 +1093,37 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>290</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F10">
         <v>290</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M10">
         <v>29000</v>
@@ -1159,7 +1132,7 @@
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -1173,37 +1146,37 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D11">
         <v>157.71</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F11">
         <v>157.71</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K11" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M11">
         <v>21000</v>
@@ -1215,7 +1188,7 @@
         <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="Q11">
         <v>540250</v>
@@ -1226,37 +1199,37 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12">
         <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F12">
         <v>116</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M12">
         <v>2000</v>
@@ -1265,7 +1238,7 @@
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="P12" t="s">
         <v>26</v>
@@ -1279,37 +1252,37 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13">
         <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F13">
         <v>224</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K13" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M13">
         <v>16000</v>
@@ -1318,7 +1291,7 @@
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="P13" t="s">
         <v>26</v>
@@ -1332,37 +1305,37 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D14">
         <v>223.4</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F14">
         <v>223.4</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I14" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J14" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K14" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L14" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M14">
         <v>10000</v>
@@ -1374,7 +1347,7 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="Q14">
         <v>1675500</v>
@@ -1385,37 +1358,37 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D15">
         <v>297</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F15">
         <v>297</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I15" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J15" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K15" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L15" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M15">
         <v>22000</v>
@@ -1424,7 +1397,7 @@
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="P15" t="s">
         <v>30</v>
@@ -1438,37 +1411,37 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D16">
         <v>2660</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F16">
         <v>2553.6</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K16" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M16">
         <v>35000</v>
@@ -1477,10 +1450,10 @@
         <v>96</v>
       </c>
       <c r="O16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q16">
         <v>9340690</v>
@@ -1491,37 +1464,37 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D17">
         <v>2660</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F17">
         <v>106.4</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K17" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M17">
         <v>35000</v>
@@ -1530,10 +1503,10 @@
         <v>4</v>
       </c>
       <c r="O17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="Q17">
         <v>9340690</v>
@@ -1544,37 +1517,37 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D18">
         <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F18">
         <v>120</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H18" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I18" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J18" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K18" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L18" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M18">
         <v>2000</v>
@@ -1583,10 +1556,10 @@
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P18" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="Q18">
         <v>4500000</v>
@@ -1597,37 +1570,37 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
         <v>49</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
       </c>
       <c r="D19">
         <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F19">
         <v>80</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I19" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J19" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K19" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L19" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M19">
         <v>2000</v>
@@ -1639,7 +1612,7 @@
         <v>31</v>
       </c>
       <c r="P19" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Q19">
         <v>3000000</v>
@@ -1650,37 +1623,37 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D20">
         <v>161.8</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F20">
         <v>161.8</v>
       </c>
       <c r="G20" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I20" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J20" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L20" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="M20">
         <v>10000</v>
@@ -1689,278 +1662,13 @@
         <v>100</v>
       </c>
       <c r="O20" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="P20" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="Q20">
         <v>1187900</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21">
-        <v>4350</v>
-      </c>
-      <c r="E21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21">
-        <v>1435.5</v>
-      </c>
-      <c r="G21" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" t="s">
-        <v>69</v>
-      </c>
-      <c r="J21" t="s">
-        <v>69</v>
-      </c>
-      <c r="K21" t="s">
-        <v>70</v>
-      </c>
-      <c r="L21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M21">
-        <v>60000</v>
-      </c>
-      <c r="N21">
-        <v>33</v>
-      </c>
-      <c r="O21" t="s">
-        <v>80</v>
-      </c>
-      <c r="P21" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q21">
-        <v>21750000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
-      <c r="A22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22">
-        <v>4350</v>
-      </c>
-      <c r="E22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22">
-        <v>1435.5</v>
-      </c>
-      <c r="G22" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" t="s">
-        <v>69</v>
-      </c>
-      <c r="J22" t="s">
-        <v>69</v>
-      </c>
-      <c r="K22" t="s">
-        <v>70</v>
-      </c>
-      <c r="L22" t="s">
-        <v>69</v>
-      </c>
-      <c r="M22">
-        <v>60000</v>
-      </c>
-      <c r="N22">
-        <v>33</v>
-      </c>
-      <c r="O22" t="s">
-        <v>80</v>
-      </c>
-      <c r="P22" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q22">
-        <v>21750000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23">
-        <v>4350</v>
-      </c>
-      <c r="E23" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23">
-        <v>1305</v>
-      </c>
-      <c r="G23" t="s">
-        <v>69</v>
-      </c>
-      <c r="H23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" t="s">
-        <v>69</v>
-      </c>
-      <c r="J23" t="s">
-        <v>69</v>
-      </c>
-      <c r="K23" t="s">
-        <v>70</v>
-      </c>
-      <c r="L23" t="s">
-        <v>69</v>
-      </c>
-      <c r="M23">
-        <v>60000</v>
-      </c>
-      <c r="N23">
-        <v>30</v>
-      </c>
-      <c r="O23" t="s">
-        <v>80</v>
-      </c>
-      <c r="P23" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q23">
-        <v>21750000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24">
-        <v>4350</v>
-      </c>
-      <c r="E24" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24">
-        <v>174</v>
-      </c>
-      <c r="G24" t="s">
-        <v>69</v>
-      </c>
-      <c r="H24" t="s">
-        <v>69</v>
-      </c>
-      <c r="I24" t="s">
-        <v>69</v>
-      </c>
-      <c r="J24" t="s">
-        <v>69</v>
-      </c>
-      <c r="K24" t="s">
-        <v>71</v>
-      </c>
-      <c r="L24" t="s">
-        <v>69</v>
-      </c>
-      <c r="M24">
-        <v>60000</v>
-      </c>
-      <c r="N24">
-        <v>4</v>
-      </c>
-      <c r="O24" t="s">
-        <v>80</v>
-      </c>
-      <c r="P24" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q24">
-        <v>21750000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25">
-        <v>80</v>
-      </c>
-      <c r="E25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25">
-        <v>80</v>
-      </c>
-      <c r="G25" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" t="s">
-        <v>69</v>
-      </c>
-      <c r="J25" t="s">
-        <v>69</v>
-      </c>
-      <c r="K25" t="s">
-        <v>70</v>
-      </c>
-      <c r="L25" t="s">
-        <v>69</v>
-      </c>
-      <c r="M25">
-        <v>2000</v>
-      </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25" t="s">
-        <v>80</v>
-      </c>
-      <c r="P25" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q25">
-        <v>3000000</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="76">
   <si>
     <t>상장일</t>
   </si>
@@ -109,132 +109,126 @@
     <t>2024-07-25</t>
   </si>
   <si>
+    <t>아이스크림미디어</t>
+  </si>
+  <si>
+    <t>M83</t>
+  </si>
+  <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
+    <t>케이쓰리아이</t>
+  </si>
+  <si>
+    <t>넥스트바이오메디컬</t>
+  </si>
+  <si>
+    <t>유라클</t>
+  </si>
+  <si>
+    <t>교보16호스팩</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
+    <t>아이빔테크놀로지</t>
+  </si>
+  <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
+    <t>SK증권제13호스팩</t>
+  </si>
+  <si>
+    <t>코스닥</t>
+  </si>
+  <si>
+    <t>코스피</t>
+  </si>
+  <si>
+    <t>삼성</t>
+  </si>
+  <si>
+    <t>신영</t>
+  </si>
+  <si>
+    <t>유진</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>대신</t>
+  </si>
+  <si>
+    <t>미래</t>
+  </si>
+  <si>
+    <t>하나</t>
+  </si>
+  <si>
+    <t>키움</t>
+  </si>
+  <si>
+    <t>교보</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>대표</t>
+  </si>
+  <si>
+    <t>인수</t>
+  </si>
+  <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
+    <t>2024-08-07</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
+    <t>2024-07-22</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>2024-07-16</t>
+  </si>
+  <si>
     <t>2024-07-15</t>
   </si>
   <si>
-    <t>아이스크림미디어</t>
-  </si>
-  <si>
-    <t>M83</t>
-  </si>
-  <si>
-    <t>이엔셀</t>
-  </si>
-  <si>
-    <t>티디에스팜</t>
-  </si>
-  <si>
-    <t>대신밸런스제18호스팩</t>
-  </si>
-  <si>
-    <t>전진건설로봇</t>
-  </si>
-  <si>
-    <t>케이쓰리아이</t>
-  </si>
-  <si>
-    <t>넥스트바이오메디컬</t>
-  </si>
-  <si>
-    <t>유라클</t>
-  </si>
-  <si>
-    <t>교보16호스팩</t>
-  </si>
-  <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
-    <t>아이빔테크놀로지</t>
-  </si>
-  <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
-    <t>코스닥</t>
-  </si>
-  <si>
-    <t>코스피</t>
-  </si>
-  <si>
-    <t>삼성</t>
-  </si>
-  <si>
-    <t>신영</t>
-  </si>
-  <si>
-    <t>유진</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>한국</t>
-  </si>
-  <si>
-    <t>대신</t>
-  </si>
-  <si>
-    <t>미래</t>
-  </si>
-  <si>
-    <t>하나</t>
-  </si>
-  <si>
-    <t>키움</t>
-  </si>
-  <si>
-    <t>교보</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>대표</t>
-  </si>
-  <si>
-    <t>인수</t>
-  </si>
-  <si>
-    <t>2024-08-09</t>
-  </si>
-  <si>
-    <t>2024-08-08</t>
-  </si>
-  <si>
-    <t>2024-08-07</t>
-  </si>
-  <si>
-    <t>2024-08-01</t>
-  </si>
-  <si>
-    <t>2024-07-22</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
     <t>2024-08-26</t>
   </si>
   <si>
@@ -248,9 +242,6 @@
   </si>
   <si>
     <t>2024-07-19</t>
-  </si>
-  <si>
-    <t>2024-07-08</t>
   </si>
 </sst>
 </file>
@@ -608,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -669,37 +660,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D2">
         <v>787.2</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2">
         <v>787.2</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M2">
         <v>32000</v>
@@ -711,7 +702,7 @@
         <v>20</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Q2">
         <v>1722000</v>
@@ -722,37 +713,37 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3">
         <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>228</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M3">
         <v>16000</v>
@@ -775,37 +766,37 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D4">
         <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F4">
         <v>12</v>
       </c>
       <c r="G4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" t="s">
         <v>62</v>
       </c>
-      <c r="H4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J4" t="s">
-        <v>62</v>
-      </c>
-      <c r="K4" t="s">
-        <v>64</v>
-      </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M4">
         <v>16000</v>
@@ -828,37 +819,37 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>239.7204</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5">
         <v>239.7204</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M5">
         <v>15300</v>
@@ -881,37 +872,37 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F6">
         <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M6">
         <v>13000</v>
@@ -920,10 +911,10 @@
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q6">
         <v>723700</v>
@@ -934,37 +925,37 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F7">
         <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M7">
         <v>2000</v>
@@ -973,10 +964,10 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q7">
         <v>4875000</v>
@@ -987,37 +978,37 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>507.81225</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8">
         <v>507.81225</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M8">
         <v>16500</v>
@@ -1026,7 +1017,7 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P8" t="s">
         <v>24</v>
@@ -1040,37 +1031,37 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9">
         <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9">
         <v>217</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M9">
         <v>15500</v>
@@ -1079,7 +1070,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P9" t="s">
         <v>24</v>
@@ -1093,37 +1084,37 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>290</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F10">
         <v>290</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M10">
         <v>29000</v>
@@ -1132,7 +1123,7 @@
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -1146,37 +1137,37 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11">
         <v>157.71</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F11">
         <v>157.71</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M11">
         <v>21000</v>
@@ -1188,7 +1179,7 @@
         <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q11">
         <v>540250</v>
@@ -1199,37 +1190,37 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F12">
         <v>116</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M12">
         <v>2000</v>
@@ -1238,7 +1229,7 @@
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P12" t="s">
         <v>26</v>
@@ -1252,37 +1243,37 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F13">
         <v>224</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M13">
         <v>16000</v>
@@ -1291,7 +1282,7 @@
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P13" t="s">
         <v>26</v>
@@ -1305,37 +1296,37 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <v>223.4</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F14">
         <v>223.4</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M14">
         <v>10000</v>
@@ -1347,7 +1338,7 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q14">
         <v>1675500</v>
@@ -1358,37 +1349,37 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>297</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F15">
         <v>297</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M15">
         <v>22000</v>
@@ -1397,7 +1388,7 @@
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P15" t="s">
         <v>30</v>
@@ -1411,37 +1402,37 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16">
         <v>2660</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F16">
         <v>2553.6</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M16">
         <v>35000</v>
@@ -1450,10 +1441,10 @@
         <v>96</v>
       </c>
       <c r="O16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q16">
         <v>9340690</v>
@@ -1464,37 +1455,37 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17">
         <v>2660</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17">
         <v>106.4</v>
       </c>
       <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" t="s">
+        <v>60</v>
+      </c>
+      <c r="K17" t="s">
         <v>62</v>
       </c>
-      <c r="H17" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17" t="s">
-        <v>62</v>
-      </c>
-      <c r="K17" t="s">
-        <v>64</v>
-      </c>
       <c r="L17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M17">
         <v>35000</v>
@@ -1503,10 +1494,10 @@
         <v>4</v>
       </c>
       <c r="O17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q17">
         <v>9340690</v>
@@ -1517,37 +1508,37 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D18">
         <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F18">
         <v>120</v>
       </c>
       <c r="G18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M18">
         <v>2000</v>
@@ -1556,10 +1547,10 @@
         <v>100</v>
       </c>
       <c r="O18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q18">
         <v>4500000</v>
@@ -1570,37 +1561,37 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
         <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
       </c>
       <c r="D19">
         <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F19">
         <v>80</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M19">
         <v>2000</v>
@@ -1609,66 +1600,13 @@
         <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="Q19">
         <v>3000000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20">
-        <v>161.8</v>
-      </c>
-      <c r="E20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20">
-        <v>161.8</v>
-      </c>
-      <c r="G20" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" t="s">
-        <v>62</v>
-      </c>
-      <c r="K20" t="s">
-        <v>63</v>
-      </c>
-      <c r="L20" t="s">
-        <v>62</v>
-      </c>
-      <c r="M20">
-        <v>10000</v>
-      </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
-      <c r="O20" t="s">
-        <v>72</v>
-      </c>
-      <c r="P20" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q20">
-        <v>1187900</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="80">
   <si>
     <t>상장일</t>
   </si>
@@ -67,6 +67,9 @@
     <t>총기관배정수량</t>
   </si>
   <si>
+    <t>2024-09-11</t>
+  </si>
+  <si>
     <t>2024-08-30</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>2024-07-25</t>
   </si>
   <si>
+    <t>미래에셋비전스팩7호</t>
+  </si>
+  <si>
     <t>아이스크림미디어</t>
   </si>
   <si>
@@ -163,6 +169,9 @@
     <t>코스피</t>
   </si>
   <si>
+    <t>미래</t>
+  </si>
+  <si>
     <t>삼성</t>
   </si>
   <si>
@@ -181,9 +190,6 @@
     <t>대신</t>
   </si>
   <si>
-    <t>미래</t>
-  </si>
-  <si>
     <t>하나</t>
   </si>
   <si>
@@ -205,6 +211,9 @@
     <t>인수</t>
   </si>
   <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
     <t>2024-08-09</t>
   </si>
   <si>
@@ -227,6 +236,9 @@
   </si>
   <si>
     <t>2024-07-15</t>
+  </si>
+  <si>
+    <t>2024-09-05</t>
   </si>
   <si>
     <t>2024-08-26</t>
@@ -599,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -660,52 +672,52 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>787.2</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F2">
-        <v>787.2</v>
+        <v>159</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M2">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="N2">
         <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q2">
-        <v>1722000</v>
+        <v>5962500</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -713,102 +725,102 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>240</v>
+        <v>787.2</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F3">
-        <v>228</v>
+        <v>787.2</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M3">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="N3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P3" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="Q3">
-        <v>2100000</v>
+        <v>1722000</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4">
         <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M4">
         <v>16000</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="O4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q4">
         <v>2100000</v>
@@ -819,52 +831,52 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>239.7204</v>
+        <v>240</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5">
-        <v>239.7204</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M5">
-        <v>15300</v>
+        <v>16000</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q5">
-        <v>1156798</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -872,158 +884,158 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M6">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="P6" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="Q6">
-        <v>723700</v>
+        <v>1156798</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7">
         <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M7">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="Q7">
-        <v>4875000</v>
+        <v>723700</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F8">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M8">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P8" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="Q8">
-        <v>2078175</v>
+        <v>4875000</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1031,105 +1043,105 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F9">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M9">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q9">
-        <v>1050000</v>
+        <v>2078175</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F10">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M10">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
       </c>
       <c r="Q10">
-        <v>720000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1137,52 +1149,52 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F11">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M11">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11" t="s">
+        <v>68</v>
+      </c>
+      <c r="P11" t="s">
         <v>26</v>
       </c>
-      <c r="P11" t="s">
-        <v>63</v>
-      </c>
       <c r="Q11">
-        <v>540250</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1190,52 +1202,52 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M12">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" t="s">
         <v>66</v>
       </c>
-      <c r="P12" t="s">
-        <v>26</v>
-      </c>
       <c r="Q12">
-        <v>4350000</v>
+        <v>540250</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1243,52 +1255,52 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F13">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M13">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="P13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q13">
-        <v>1050000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1296,52 +1308,52 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F14">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M14">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="P14" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="Q14">
-        <v>1675500</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1349,52 +1361,52 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F15">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M15">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="P15" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="Q15">
-        <v>1012500</v>
+        <v>1675500</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1402,102 +1414,102 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16">
-        <v>2660</v>
+        <v>297</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F16">
-        <v>2553.6</v>
+        <v>297</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M16">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="N16">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P16" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="Q16">
-        <v>9340690</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D17">
         <v>2660</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F17">
-        <v>106.4</v>
+        <v>2553.6</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M17">
         <v>35000</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="O17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="Q17">
         <v>9340690</v>
@@ -1508,52 +1520,52 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D18">
-        <v>120</v>
+        <v>2660</v>
       </c>
       <c r="E18" t="s">
         <v>52</v>
       </c>
       <c r="F18">
-        <v>120</v>
+        <v>106.4</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K18" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M18">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="O18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q18">
-        <v>4500000</v>
+        <v>9340690</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1561,37 +1573,37 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F19">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M19">
         <v>2000</v>
@@ -1600,12 +1612,65 @@
         <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P19" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="Q19">
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20">
+        <v>80</v>
+      </c>
+      <c r="E20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" t="s">
+        <v>62</v>
+      </c>
+      <c r="J20" t="s">
+        <v>62</v>
+      </c>
+      <c r="K20" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20">
+        <v>2000</v>
+      </c>
+      <c r="N20">
+        <v>100</v>
+      </c>
+      <c r="O20" t="s">
+        <v>73</v>
+      </c>
+      <c r="P20" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q20">
         <v>3000000</v>
       </c>
     </row>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="77">
   <si>
     <t>상장일</t>
   </si>
@@ -109,123 +109,117 @@
     <t>2024-07-26</t>
   </si>
   <si>
+    <t>미래에셋비전스팩7호</t>
+  </si>
+  <si>
+    <t>아이스크림미디어</t>
+  </si>
+  <si>
+    <t>M83</t>
+  </si>
+  <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
+    <t>티디에스팜</t>
+  </si>
+  <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
+    <t>전진건설로봇</t>
+  </si>
+  <si>
+    <t>케이쓰리아이</t>
+  </si>
+  <si>
+    <t>넥스트바이오메디컬</t>
+  </si>
+  <si>
+    <t>유라클</t>
+  </si>
+  <si>
+    <t>교보16호스팩</t>
+  </si>
+  <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
+    <t>아이빔테크놀로지</t>
+  </si>
+  <si>
+    <t>피앤에스미캐닉스</t>
+  </si>
+  <si>
+    <t>산일전기</t>
+  </si>
+  <si>
+    <t>엔에이치스팩31호</t>
+  </si>
+  <si>
+    <t>코스닥</t>
+  </si>
+  <si>
+    <t>코스피</t>
+  </si>
+  <si>
+    <t>미래</t>
+  </si>
+  <si>
+    <t>삼성</t>
+  </si>
+  <si>
+    <t>신영</t>
+  </si>
+  <si>
+    <t>유진</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>대신</t>
+  </si>
+  <si>
+    <t>하나</t>
+  </si>
+  <si>
+    <t>키움</t>
+  </si>
+  <si>
+    <t>교보</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>대표</t>
+  </si>
+  <si>
+    <t>인수</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
+    <t>2024-08-07</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
     <t>2024-07-25</t>
   </si>
   <si>
-    <t>미래에셋비전스팩7호</t>
-  </si>
-  <si>
-    <t>아이스크림미디어</t>
-  </si>
-  <si>
-    <t>M83</t>
-  </si>
-  <si>
-    <t>이엔셀</t>
-  </si>
-  <si>
-    <t>티디에스팜</t>
-  </si>
-  <si>
-    <t>대신밸런스제18호스팩</t>
-  </si>
-  <si>
-    <t>전진건설로봇</t>
-  </si>
-  <si>
-    <t>케이쓰리아이</t>
-  </si>
-  <si>
-    <t>넥스트바이오메디컬</t>
-  </si>
-  <si>
-    <t>유라클</t>
-  </si>
-  <si>
-    <t>교보16호스팩</t>
-  </si>
-  <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
-    <t>아이빔테크놀로지</t>
-  </si>
-  <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
-    <t>산일전기</t>
-  </si>
-  <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
-    <t>코스닥</t>
-  </si>
-  <si>
-    <t>코스피</t>
-  </si>
-  <si>
-    <t>미래</t>
-  </si>
-  <si>
-    <t>삼성</t>
-  </si>
-  <si>
-    <t>신영</t>
-  </si>
-  <si>
-    <t>유진</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>한국</t>
-  </si>
-  <si>
-    <t>대신</t>
-  </si>
-  <si>
-    <t>하나</t>
-  </si>
-  <si>
-    <t>키움</t>
-  </si>
-  <si>
-    <t>교보</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>대표</t>
-  </si>
-  <si>
-    <t>인수</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>2024-08-09</t>
-  </si>
-  <si>
-    <t>2024-08-08</t>
-  </si>
-  <si>
-    <t>2024-08-07</t>
-  </si>
-  <si>
-    <t>2024-08-01</t>
-  </si>
-  <si>
     <t>2024-07-22</t>
   </si>
   <si>
@@ -233,9 +227,6 @@
   </si>
   <si>
     <t>2024-07-16</t>
-  </si>
-  <si>
-    <t>2024-07-15</t>
   </si>
   <si>
     <t>2024-09-05</t>
@@ -611,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -672,37 +663,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D2">
         <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2">
         <v>159</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M2">
         <v>2000</v>
@@ -711,10 +702,10 @@
         <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q2">
         <v>5962500</v>
@@ -725,37 +716,37 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3">
         <v>787.2</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>787.2</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M3">
         <v>32000</v>
@@ -767,7 +758,7 @@
         <v>21</v>
       </c>
       <c r="P3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Q3">
         <v>1722000</v>
@@ -778,37 +769,37 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D4">
         <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F4">
         <v>228</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M4">
         <v>16000</v>
@@ -831,37 +822,37 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>240</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M5">
         <v>16000</v>
@@ -884,37 +875,37 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>239.7204</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F6">
         <v>239.7204</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M6">
         <v>15300</v>
@@ -937,37 +928,37 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F7">
         <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M7">
         <v>13000</v>
@@ -976,10 +967,10 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q7">
         <v>723700</v>
@@ -990,37 +981,37 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8">
         <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8">
         <v>130</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M8">
         <v>2000</v>
@@ -1029,10 +1020,10 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q8">
         <v>4875000</v>
@@ -1043,37 +1034,37 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>507.81225</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9">
         <v>507.81225</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M9">
         <v>16500</v>
@@ -1082,7 +1073,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -1096,37 +1087,37 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F10">
         <v>217</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M10">
         <v>15500</v>
@@ -1135,7 +1126,7 @@
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -1149,37 +1140,37 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11">
         <v>290</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F11">
         <v>290</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M11">
         <v>29000</v>
@@ -1188,7 +1179,7 @@
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P11" t="s">
         <v>26</v>
@@ -1202,37 +1193,37 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>157.71</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F12">
         <v>157.71</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M12">
         <v>21000</v>
@@ -1244,7 +1235,7 @@
         <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="Q12">
         <v>540250</v>
@@ -1255,37 +1246,37 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F13">
         <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M13">
         <v>2000</v>
@@ -1294,7 +1285,7 @@
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P13" t="s">
         <v>27</v>
@@ -1308,37 +1299,37 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F14">
         <v>224</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M14">
         <v>16000</v>
@@ -1347,7 +1338,7 @@
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P14" t="s">
         <v>27</v>
@@ -1361,37 +1352,37 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>223.4</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F15">
         <v>223.4</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M15">
         <v>10000</v>
@@ -1400,10 +1391,10 @@
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="P15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q15">
         <v>1675500</v>
@@ -1414,37 +1405,37 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16">
         <v>297</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F16">
         <v>297</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M16">
         <v>22000</v>
@@ -1453,10 +1444,10 @@
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P16" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="Q16">
         <v>1012500</v>
@@ -1467,37 +1458,37 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17">
         <v>2660</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17">
         <v>2553.6</v>
       </c>
       <c r="G17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M17">
         <v>35000</v>
@@ -1506,10 +1497,10 @@
         <v>96</v>
       </c>
       <c r="O17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q17">
         <v>9340690</v>
@@ -1520,37 +1511,37 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18">
         <v>2660</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F18">
         <v>106.4</v>
       </c>
       <c r="G18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M18">
         <v>35000</v>
@@ -1559,10 +1550,10 @@
         <v>4</v>
       </c>
       <c r="O18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q18">
         <v>9340690</v>
@@ -1573,37 +1564,37 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
         <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
       </c>
       <c r="D19">
         <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F19">
         <v>120</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M19">
         <v>2000</v>
@@ -1612,66 +1603,13 @@
         <v>100</v>
       </c>
       <c r="O19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q19">
         <v>4500000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20">
-        <v>80</v>
-      </c>
-      <c r="G20" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" t="s">
-        <v>62</v>
-      </c>
-      <c r="K20" t="s">
-        <v>63</v>
-      </c>
-      <c r="L20" t="s">
-        <v>62</v>
-      </c>
-      <c r="M20">
-        <v>2000</v>
-      </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
-      <c r="O20" t="s">
-        <v>73</v>
-      </c>
-      <c r="P20" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q20">
-        <v>3000000</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="73">
   <si>
     <t>상장일</t>
   </si>
@@ -106,9 +106,6 @@
     <t>2024-07-29</t>
   </si>
   <si>
-    <t>2024-07-26</t>
-  </si>
-  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -154,9 +151,6 @@
     <t>산일전기</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
     <t>코스닥</t>
   </si>
   <si>
@@ -226,9 +220,6 @@
     <t>2024-07-18</t>
   </si>
   <si>
-    <t>2024-07-16</t>
-  </si>
-  <si>
     <t>2024-09-05</t>
   </si>
   <si>
@@ -242,9 +233,6 @@
   </si>
   <si>
     <t>2024-07-23</t>
-  </si>
-  <si>
-    <t>2024-07-19</t>
   </si>
 </sst>
 </file>
@@ -602,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -663,37 +651,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2">
         <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F2">
         <v>159</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M2">
         <v>2000</v>
@@ -702,10 +690,10 @@
         <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q2">
         <v>5962500</v>
@@ -716,37 +704,37 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>787.2</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F3">
         <v>787.2</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M3">
         <v>32000</v>
@@ -758,7 +746,7 @@
         <v>21</v>
       </c>
       <c r="P3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q3">
         <v>1722000</v>
@@ -769,37 +757,37 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4">
         <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4">
         <v>228</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M4">
         <v>16000</v>
@@ -822,37 +810,37 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>240</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5">
         <v>12</v>
       </c>
       <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
         <v>59</v>
       </c>
-      <c r="H5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" t="s">
-        <v>61</v>
-      </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M5">
         <v>16000</v>
@@ -875,37 +863,37 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>239.7204</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F6">
         <v>239.7204</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M6">
         <v>15300</v>
@@ -928,37 +916,37 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7">
         <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7">
         <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M7">
         <v>13000</v>
@@ -967,10 +955,10 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q7">
         <v>723700</v>
@@ -981,37 +969,37 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8">
         <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F8">
         <v>130</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M8">
         <v>2000</v>
@@ -1020,10 +1008,10 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q8">
         <v>4875000</v>
@@ -1034,37 +1022,37 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9">
         <v>507.81225</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>507.81225</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M9">
         <v>16500</v>
@@ -1073,7 +1061,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -1087,37 +1075,37 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10">
         <v>217</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M10">
         <v>15500</v>
@@ -1126,7 +1114,7 @@
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -1140,37 +1128,37 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11">
         <v>290</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F11">
         <v>290</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M11">
         <v>29000</v>
@@ -1179,7 +1167,7 @@
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P11" t="s">
         <v>26</v>
@@ -1193,37 +1181,37 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12">
         <v>157.71</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F12">
         <v>157.71</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M12">
         <v>21000</v>
@@ -1235,7 +1223,7 @@
         <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q12">
         <v>540250</v>
@@ -1246,37 +1234,37 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13">
         <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F13">
         <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M13">
         <v>2000</v>
@@ -1285,7 +1273,7 @@
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P13" t="s">
         <v>27</v>
@@ -1299,37 +1287,37 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14">
         <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>224</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M14">
         <v>16000</v>
@@ -1338,7 +1326,7 @@
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P14" t="s">
         <v>27</v>
@@ -1352,37 +1340,37 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15">
         <v>223.4</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F15">
         <v>223.4</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M15">
         <v>10000</v>
@@ -1391,10 +1379,10 @@
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q15">
         <v>1675500</v>
@@ -1405,37 +1393,37 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16">
         <v>297</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F16">
         <v>297</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M16">
         <v>22000</v>
@@ -1444,10 +1432,10 @@
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q16">
         <v>1012500</v>
@@ -1458,37 +1446,37 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D17">
         <v>2660</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F17">
         <v>2553.6</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M17">
         <v>35000</v>
@@ -1497,10 +1485,10 @@
         <v>96</v>
       </c>
       <c r="O17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Q17">
         <v>9340690</v>
@@ -1511,37 +1499,37 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D18">
         <v>2660</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F18">
         <v>106.4</v>
       </c>
       <c r="G18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" t="s">
         <v>59</v>
       </c>
-      <c r="H18" t="s">
-        <v>59</v>
-      </c>
-      <c r="I18" t="s">
-        <v>59</v>
-      </c>
-      <c r="J18" t="s">
-        <v>59</v>
-      </c>
-      <c r="K18" t="s">
-        <v>61</v>
-      </c>
       <c r="L18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M18">
         <v>35000</v>
@@ -1550,66 +1538,13 @@
         <v>4</v>
       </c>
       <c r="O18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Q18">
         <v>9340690</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19">
-        <v>120</v>
-      </c>
-      <c r="G19" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" t="s">
-        <v>59</v>
-      </c>
-      <c r="I19" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19" t="s">
-        <v>59</v>
-      </c>
-      <c r="K19" t="s">
-        <v>60</v>
-      </c>
-      <c r="L19" t="s">
-        <v>59</v>
-      </c>
-      <c r="M19">
-        <v>2000</v>
-      </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
-      <c r="O19" t="s">
-        <v>70</v>
-      </c>
-      <c r="P19" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q19">
-        <v>4500000</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="69">
   <si>
     <t>상장일</t>
   </si>
@@ -103,9 +103,6 @@
     <t>2024-07-31</t>
   </si>
   <si>
-    <t>2024-07-29</t>
-  </si>
-  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -148,9 +145,6 @@
     <t>피앤에스미캐닉스</t>
   </si>
   <si>
-    <t>산일전기</t>
-  </si>
-  <si>
     <t>코스닥</t>
   </si>
   <si>
@@ -217,9 +211,6 @@
     <t>2024-07-22</t>
   </si>
   <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
     <t>2024-09-05</t>
   </si>
   <si>
@@ -230,9 +221,6 @@
   </si>
   <si>
     <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>2024-07-23</t>
   </si>
 </sst>
 </file>
@@ -590,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -651,37 +639,37 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F2">
         <v>159</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M2">
         <v>2000</v>
@@ -690,10 +678,10 @@
         <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="Q2">
         <v>5962500</v>
@@ -704,37 +692,37 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3">
         <v>787.2</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>787.2</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M3">
         <v>32000</v>
@@ -746,7 +734,7 @@
         <v>21</v>
       </c>
       <c r="P3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q3">
         <v>1722000</v>
@@ -757,37 +745,37 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4">
         <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F4">
         <v>228</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M4">
         <v>16000</v>
@@ -810,37 +798,37 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>240</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F5">
         <v>12</v>
       </c>
       <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" t="s">
         <v>57</v>
       </c>
-      <c r="H5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" t="s">
-        <v>59</v>
-      </c>
       <c r="L5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M5">
         <v>16000</v>
@@ -863,37 +851,37 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6">
         <v>239.7204</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6">
         <v>239.7204</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M6">
         <v>15300</v>
@@ -916,37 +904,37 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7">
         <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M7">
         <v>13000</v>
@@ -955,10 +943,10 @@
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Q7">
         <v>723700</v>
@@ -969,37 +957,37 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F8">
         <v>130</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M8">
         <v>2000</v>
@@ -1008,10 +996,10 @@
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Q8">
         <v>4875000</v>
@@ -1022,37 +1010,37 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9">
         <v>507.81225</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F9">
         <v>507.81225</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M9">
         <v>16500</v>
@@ -1061,7 +1049,7 @@
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -1075,37 +1063,37 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D10">
         <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F10">
         <v>217</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M10">
         <v>15500</v>
@@ -1114,7 +1102,7 @@
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -1128,37 +1116,37 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D11">
         <v>290</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>290</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M11">
         <v>29000</v>
@@ -1167,7 +1155,7 @@
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P11" t="s">
         <v>26</v>
@@ -1181,37 +1169,37 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12">
         <v>157.71</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F12">
         <v>157.71</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M12">
         <v>21000</v>
@@ -1223,7 +1211,7 @@
         <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Q12">
         <v>540250</v>
@@ -1234,37 +1222,37 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13">
         <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F13">
         <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M13">
         <v>2000</v>
@@ -1273,7 +1261,7 @@
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P13" t="s">
         <v>27</v>
@@ -1287,37 +1275,37 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D14">
         <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F14">
         <v>224</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M14">
         <v>16000</v>
@@ -1326,7 +1314,7 @@
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P14" t="s">
         <v>27</v>
@@ -1340,37 +1328,37 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15">
         <v>223.4</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F15">
         <v>223.4</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M15">
         <v>10000</v>
@@ -1379,10 +1367,10 @@
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q15">
         <v>1675500</v>
@@ -1393,37 +1381,37 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
       </c>
       <c r="D16">
         <v>297</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F16">
         <v>297</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M16">
         <v>22000</v>
@@ -1432,119 +1420,13 @@
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q16">
         <v>1012500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17">
-        <v>2660</v>
-      </c>
-      <c r="E17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17">
-        <v>2553.6</v>
-      </c>
-      <c r="G17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" t="s">
-        <v>57</v>
-      </c>
-      <c r="J17" t="s">
-        <v>57</v>
-      </c>
-      <c r="K17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L17" t="s">
-        <v>57</v>
-      </c>
-      <c r="M17">
-        <v>35000</v>
-      </c>
-      <c r="N17">
-        <v>96</v>
-      </c>
-      <c r="O17" t="s">
-        <v>67</v>
-      </c>
-      <c r="P17" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q17">
-        <v>9340690</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18">
-        <v>2660</v>
-      </c>
-      <c r="E18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18">
-        <v>106.4</v>
-      </c>
-      <c r="G18" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" t="s">
-        <v>57</v>
-      </c>
-      <c r="J18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K18" t="s">
-        <v>59</v>
-      </c>
-      <c r="L18" t="s">
-        <v>57</v>
-      </c>
-      <c r="M18">
-        <v>35000</v>
-      </c>
-      <c r="N18">
-        <v>4</v>
-      </c>
-      <c r="O18" t="s">
-        <v>67</v>
-      </c>
-      <c r="P18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18">
-        <v>9340690</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="70">
   <si>
     <t>상장일</t>
   </si>
@@ -67,6 +67,9 @@
     <t>총기관배정수량</t>
   </si>
   <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
     <t>2024-09-11</t>
   </si>
   <si>
@@ -100,7 +103,7 @@
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2024-07-31</t>
+    <t>아이언디바이스</t>
   </si>
   <si>
     <t>미래에셋비전스팩7호</t>
@@ -142,15 +145,15 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
     <t>코스닥</t>
   </si>
   <si>
     <t>코스피</t>
   </si>
   <si>
+    <t>대신</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
@@ -169,9 +172,6 @@
     <t>한국</t>
   </si>
   <si>
-    <t>대신</t>
-  </si>
-  <si>
     <t>하나</t>
   </si>
   <si>
@@ -190,6 +190,9 @@
     <t>인수</t>
   </si>
   <si>
+    <t>2024-09-09</t>
+  </si>
+  <si>
     <t>2024-09-02</t>
   </si>
   <si>
@@ -208,7 +211,7 @@
     <t>2024-07-25</t>
   </si>
   <si>
-    <t>2024-07-22</t>
+    <t>2024-09-12</t>
   </si>
   <si>
     <t>2024-09-05</t>
@@ -645,13 +648,13 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="E2" t="s">
         <v>45</v>
       </c>
       <c r="F2">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="G2" t="s">
         <v>55</v>
@@ -672,7 +675,7 @@
         <v>55</v>
       </c>
       <c r="M2">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N2">
         <v>100</v>
@@ -684,7 +687,7 @@
         <v>65</v>
       </c>
       <c r="Q2">
-        <v>5962500</v>
+        <v>2187000</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -698,13 +701,13 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>787.2</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
         <v>46</v>
       </c>
       <c r="F3">
-        <v>787.2</v>
+        <v>159</v>
       </c>
       <c r="G3" t="s">
         <v>55</v>
@@ -725,19 +728,19 @@
         <v>55</v>
       </c>
       <c r="M3">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="N3">
         <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="P3" t="s">
         <v>66</v>
       </c>
       <c r="Q3">
-        <v>1722000</v>
+        <v>5962500</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -751,13 +754,13 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>240</v>
+        <v>787.2</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
       </c>
       <c r="F4">
-        <v>228</v>
+        <v>787.2</v>
       </c>
       <c r="G4" t="s">
         <v>55</v>
@@ -778,27 +781,27 @@
         <v>55</v>
       </c>
       <c r="M4">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="N4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="Q4">
-        <v>2100000</v>
+        <v>1722000</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
@@ -810,7 +813,7 @@
         <v>48</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="G5" t="s">
         <v>55</v>
@@ -825,7 +828,7 @@
         <v>55</v>
       </c>
       <c r="K5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
         <v>55</v>
@@ -834,13 +837,13 @@
         <v>16000</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q5">
         <v>2100000</v>
@@ -857,13 +860,13 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>239.7204</v>
+        <v>240</v>
       </c>
       <c r="E6" t="s">
         <v>49</v>
       </c>
       <c r="F6">
-        <v>239.7204</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>55</v>
@@ -878,25 +881,25 @@
         <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" t="s">
         <v>55</v>
       </c>
       <c r="M6">
-        <v>15300</v>
+        <v>16000</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q6">
-        <v>1156798</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -910,13 +913,13 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="E7" t="s">
         <v>50</v>
       </c>
       <c r="F7">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="G7" t="s">
         <v>55</v>
@@ -937,24 +940,24 @@
         <v>55</v>
       </c>
       <c r="M7">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="Q7">
-        <v>723700</v>
+        <v>1156798</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -990,39 +993,39 @@
         <v>55</v>
       </c>
       <c r="M8">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q8">
-        <v>4875000</v>
+        <v>723700</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
         <v>45</v>
       </c>
       <c r="F9">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="G9" t="s">
         <v>55</v>
@@ -1043,7 +1046,7 @@
         <v>55</v>
       </c>
       <c r="M9">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -1052,10 +1055,10 @@
         <v>60</v>
       </c>
       <c r="P9" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="Q9">
-        <v>2078175</v>
+        <v>4875000</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1066,16 +1069,16 @@
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F10">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="G10" t="s">
         <v>55</v>
@@ -1096,24 +1099,24 @@
         <v>55</v>
       </c>
       <c r="M10">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q10">
-        <v>1050000</v>
+        <v>2078175</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
@@ -1122,13 +1125,13 @@
         <v>43</v>
       </c>
       <c r="D11">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="G11" t="s">
         <v>55</v>
@@ -1149,7 +1152,7 @@
         <v>55</v>
       </c>
       <c r="M11">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -1161,7 +1164,7 @@
         <v>26</v>
       </c>
       <c r="Q11">
-        <v>720000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1175,13 +1178,13 @@
         <v>43</v>
       </c>
       <c r="D12">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F12">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="G12" t="s">
         <v>55</v>
@@ -1202,19 +1205,19 @@
         <v>55</v>
       </c>
       <c r="M12">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12" t="s">
+        <v>62</v>
+      </c>
+      <c r="P12" t="s">
         <v>27</v>
       </c>
-      <c r="P12" t="s">
-        <v>59</v>
-      </c>
       <c r="Q12">
-        <v>540250</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1228,13 +1231,13 @@
         <v>43</v>
       </c>
       <c r="D13">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="G13" t="s">
         <v>55</v>
@@ -1255,19 +1258,19 @@
         <v>55</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="P13" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="Q13">
-        <v>4350000</v>
+        <v>540250</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1281,13 +1284,13 @@
         <v>43</v>
       </c>
       <c r="D14">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F14">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="G14" t="s">
         <v>55</v>
@@ -1308,19 +1311,19 @@
         <v>55</v>
       </c>
       <c r="M14">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q14">
-        <v>1050000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1334,13 +1337,13 @@
         <v>43</v>
       </c>
       <c r="D15">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="E15" t="s">
         <v>46</v>
       </c>
       <c r="F15">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="G15" t="s">
         <v>55</v>
@@ -1361,7 +1364,7 @@
         <v>55</v>
       </c>
       <c r="M15">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -1370,10 +1373,10 @@
         <v>63</v>
       </c>
       <c r="P15" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="Q15">
-        <v>1675500</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1387,13 +1390,13 @@
         <v>43</v>
       </c>
       <c r="D16">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F16">
-        <v>297</v>
+        <v>223.4</v>
       </c>
       <c r="G16" t="s">
         <v>55</v>
@@ -1414,7 +1417,7 @@
         <v>55</v>
       </c>
       <c r="M16">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -1423,10 +1426,10 @@
         <v>64</v>
       </c>
       <c r="P16" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="Q16">
-        <v>1012500</v>
+        <v>1675500</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/form1.xlsx
+++ b/datasets/form1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="75">
   <si>
     <t>상장일</t>
   </si>
@@ -67,6 +67,9 @@
     <t>총기관배정수량</t>
   </si>
   <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
     <t>2024-09-23</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>2024-08-06</t>
   </si>
   <si>
+    <t>KB제30호스팩</t>
+  </si>
+  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -151,6 +157,9 @@
     <t>코스피</t>
   </si>
   <si>
+    <t>KB</t>
+  </si>
+  <si>
     <t>대신</t>
   </si>
   <si>
@@ -190,6 +199,9 @@
     <t>인수</t>
   </si>
   <si>
+    <t>2024-09-10</t>
+  </si>
+  <si>
     <t>2024-09-09</t>
   </si>
   <si>
@@ -209,6 +221,9 @@
   </si>
   <si>
     <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>2024-09-13</t>
   </si>
   <si>
     <t>2024-09-12</t>
@@ -581,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -642,52 +657,52 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M2">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="N2">
         <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Q2">
-        <v>2187000</v>
+        <v>3750000</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -695,52 +710,52 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M3">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N3">
         <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q3">
-        <v>5962500</v>
+        <v>2187000</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -748,52 +763,52 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>787.2</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4">
-        <v>787.2</v>
+        <v>159</v>
       </c>
       <c r="G4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M4">
-        <v>32000</v>
+        <v>2000</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="P4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q4">
-        <v>1722000</v>
+        <v>5962500</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -801,102 +816,102 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>240</v>
+        <v>787.2</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5">
-        <v>228</v>
+        <v>787.2</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M5">
-        <v>16000</v>
+        <v>32000</v>
       </c>
       <c r="N5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="Q5">
-        <v>2100000</v>
+        <v>1722000</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>240</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M6">
         <v>16000</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="O6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q6">
         <v>2100000</v>
@@ -907,52 +922,52 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>239.7204</v>
+        <v>240</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7">
-        <v>239.7204</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M7">
-        <v>15300</v>
+        <v>16000</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q7">
-        <v>1156798</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -960,158 +975,158 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8">
-        <v>130</v>
+        <v>239.7204</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M8">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="P8" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="Q8">
-        <v>723700</v>
+        <v>1156798</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F9">
         <v>130</v>
       </c>
       <c r="G9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M9">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="P9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q9">
-        <v>4875000</v>
+        <v>723700</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>507.81225</v>
+        <v>130</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M10">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P10" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="Q10">
-        <v>2078175</v>
+        <v>4875000</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1119,105 +1134,105 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D11">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F11">
-        <v>217</v>
+        <v>507.81225</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M11">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>1050000</v>
+        <v>2078175</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F12">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M12">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P12" t="s">
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>720000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1225,52 +1240,52 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13">
-        <v>157.71</v>
+        <v>290</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M13">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P13" t="s">
         <v>28</v>
       </c>
-      <c r="P13" t="s">
-        <v>60</v>
-      </c>
       <c r="Q13">
-        <v>540250</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1278,52 +1293,52 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F14">
-        <v>116</v>
+        <v>157.71</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M14">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="P14" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="Q14">
-        <v>4350000</v>
+        <v>540250</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1331,52 +1346,52 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F15">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M15">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q15">
-        <v>1050000</v>
+        <v>4350000</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1384,51 +1399,104 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D16">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F16">
-        <v>223.4</v>
+        <v>224</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M16">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P16" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="Q16">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17">
+        <v>223.4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17">
+        <v>223.4</v>
+      </c>
+      <c r="G17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17">
+        <v>10000</v>
+      </c>
+      <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17" t="s">
+        <v>68</v>
+      </c>
+      <c r="P17" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q17">
         <v>1675500</v>
       </c>
     </row>
